--- a/output/bases_limpias/Grupo_03_MODULOS/df_ugme_modulares.xlsx
+++ b/output/bases_limpias/Grupo_03_MODULOS/df_ugme_modulares.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P418"/>
+  <dimension ref="A1:R418"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,6 +497,16 @@
           <t>ubigeo</t>
         </is>
       </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>dre</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>ugel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -563,6 +573,16 @@
           <t>020101</t>
         </is>
       </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>UGEL HUARAZ</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -629,6 +649,16 @@
           <t>022001</t>
         </is>
       </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>UGEL YUNGAY</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -695,6 +725,16 @@
           <t>022001</t>
         </is>
       </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>UGEL YUNGAY</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -761,6 +801,16 @@
           <t>050114</t>
         </is>
       </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -827,6 +877,16 @@
           <t>050702</t>
         </is>
       </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>UGEL PARINACOCHAS</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -893,6 +953,16 @@
           <t>130502</t>
         </is>
       </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>UGEL JULCÁN</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -959,6 +1029,16 @@
           <t>130504</t>
         </is>
       </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>UGEL JULCÁN</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1025,6 +1105,16 @@
           <t>130602</t>
         </is>
       </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>UGEL OTUZCO</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1091,6 +1181,16 @@
           <t>130902</t>
         </is>
       </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>UGEL SÁNCHEZ CARRIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1161,6 +1261,16 @@
           <t>140308</t>
         </is>
       </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1227,6 +1337,16 @@
           <t>160705</t>
         </is>
       </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>UGEL ALTO AMAZONAS-SAN LORENZO</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1291,6 +1411,16 @@
           <t>160705</t>
         </is>
       </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>UGEL ALTO AMAZONAS-SAN LORENZO</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1357,6 +1487,16 @@
           <t>160502</t>
         </is>
       </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>UGEL REQUENA</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1421,6 +1561,16 @@
           <t>160502</t>
         </is>
       </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>UGEL REQUENA</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1487,6 +1637,16 @@
           <t>160508</t>
         </is>
       </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>UGEL REQUENA</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1551,6 +1711,16 @@
           <t>160508</t>
         </is>
       </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>UGEL REQUENA</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1617,6 +1787,16 @@
           <t>160604</t>
         </is>
       </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>UGEL UCAYALI-CONTAMANA</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1681,6 +1861,16 @@
           <t>160604</t>
         </is>
       </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>UGEL UCAYALI-CONTAMANA</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1747,6 +1937,16 @@
           <t>200115</t>
         </is>
       </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1813,6 +2013,16 @@
           <t>200110</t>
         </is>
       </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>UGEL LA UNIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1879,6 +2089,16 @@
           <t>200201</t>
         </is>
       </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>UGEL AYABACA</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1945,6 +2165,16 @@
           <t>200201</t>
         </is>
       </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>UGEL AYABACA</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2011,6 +2241,16 @@
           <t>200201</t>
         </is>
       </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>UGEL AYABACA</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2077,6 +2317,16 @@
           <t>200201</t>
         </is>
       </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>UGEL AYABACA</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2143,6 +2393,16 @@
           <t>200201</t>
         </is>
       </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>UGEL AYABACA</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2209,6 +2469,16 @@
           <t>200203</t>
         </is>
       </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>UGEL AYABACA</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2275,6 +2545,16 @@
           <t>200203</t>
         </is>
       </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>UGEL AYABACA</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2341,6 +2621,16 @@
           <t>200301</t>
         </is>
       </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>UGEL HUANCABAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2407,6 +2697,16 @@
           <t>200303</t>
         </is>
       </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>UGEL HUANCABAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2473,6 +2773,16 @@
           <t>200303</t>
         </is>
       </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>UGEL HUANCABAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2539,6 +2849,16 @@
           <t>200304</t>
         </is>
       </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>UGEL HUARMACA</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2605,6 +2925,16 @@
           <t>200304</t>
         </is>
       </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>UGEL HUARMACA</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2671,6 +3001,16 @@
           <t>200304</t>
         </is>
       </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>UGEL HUARMACA</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2737,6 +3077,16 @@
           <t>200304</t>
         </is>
       </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>UGEL HUARMACA</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2803,6 +3153,16 @@
           <t>200304</t>
         </is>
       </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>UGEL HUARMACA</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2869,6 +3229,16 @@
           <t>200304</t>
         </is>
       </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>UGEL HUARMACA</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2935,6 +3305,16 @@
           <t>200304</t>
         </is>
       </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>UGEL HUARMACA</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3001,6 +3381,16 @@
           <t>200304</t>
         </is>
       </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>UGEL HUARMACA</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3067,6 +3457,16 @@
           <t>200304</t>
         </is>
       </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>UGEL HUARMACA</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3133,6 +3533,16 @@
           <t>200401</t>
         </is>
       </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>UGEL CHULUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -3199,6 +3609,16 @@
           <t>200405</t>
         </is>
       </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>UGEL CHULUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -3265,6 +3685,16 @@
           <t>200401</t>
         </is>
       </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>UGEL CHULUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -3331,6 +3761,16 @@
           <t>200401</t>
         </is>
       </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>UGEL CHULUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3397,6 +3837,16 @@
           <t>200401</t>
         </is>
       </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>UGEL CHULUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3463,6 +3913,16 @@
           <t>200401</t>
         </is>
       </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>UGEL CHULUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3529,6 +3989,16 @@
           <t>200407</t>
         </is>
       </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>UGEL MORROPÓN</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3595,6 +4065,16 @@
           <t>200407</t>
         </is>
       </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>UGEL MORROPÓN</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3661,6 +4141,16 @@
           <t>200601</t>
         </is>
       </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>UGEL SULLANA</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3727,6 +4217,16 @@
           <t>200601</t>
         </is>
       </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>UGEL SULLANA</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3793,6 +4293,16 @@
           <t>200603</t>
         </is>
       </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>UGEL SULLANA</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3859,6 +4369,16 @@
           <t>200706</t>
         </is>
       </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>UGEL CONTRALMIRANTE VILLAR</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3925,6 +4445,16 @@
           <t>200802</t>
         </is>
       </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>UGEL SECHURA</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -3991,6 +4521,16 @@
           <t>240101</t>
         </is>
       </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>UGEL TUMBES</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -4057,6 +4597,16 @@
           <t>240101</t>
         </is>
       </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>UGEL TUMBES</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -4123,6 +4673,16 @@
           <t>240101</t>
         </is>
       </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>UGEL TUMBES</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -4189,6 +4749,16 @@
           <t>240101</t>
         </is>
       </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>UGEL TUMBES</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -4255,6 +4825,16 @@
           <t>240101</t>
         </is>
       </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>UGEL TUMBES</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -4321,6 +4901,16 @@
           <t>240102</t>
         </is>
       </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>UGEL TUMBES</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -4387,6 +4977,16 @@
           <t>240103</t>
         </is>
       </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>UGEL CONTRALMIRANTE VILLAR</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -4451,6 +5051,16 @@
       <c r="P61" t="inlineStr">
         <is>
           <t>240104</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>UGEL TUMBES</t>
         </is>
       </c>
     </row>
@@ -4519,6 +5129,16 @@
           <t>200201</t>
         </is>
       </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>UGEL AYABACA</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -4585,6 +5205,16 @@
           <t>200201</t>
         </is>
       </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>UGEL AYABACA</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -4651,6 +5281,16 @@
           <t>200114</t>
         </is>
       </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOGRANDE</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -4717,6 +5357,16 @@
           <t>160705</t>
         </is>
       </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>UGEL ALTO AMAZONAS-SAN LORENZO</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -4781,6 +5431,16 @@
           <t>160705</t>
         </is>
       </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>UGEL ALTO AMAZONAS-SAN LORENZO</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -4847,6 +5507,16 @@
           <t>160705</t>
         </is>
       </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>UGEL ALTO AMAZONAS-SAN LORENZO</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -4911,6 +5581,16 @@
           <t>160705</t>
         </is>
       </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>UGEL ALTO AMAZONAS-SAN LORENZO</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -4977,6 +5657,16 @@
           <t>130902</t>
         </is>
       </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>UGEL SÁNCHEZ CARRIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -5043,6 +5733,16 @@
           <t>240203</t>
         </is>
       </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>UGEL CONTRALMIRANTE VILLAR</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -5109,6 +5809,16 @@
           <t>160501</t>
         </is>
       </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>UGEL REQUENA</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -5173,6 +5883,16 @@
           <t>160501</t>
         </is>
       </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>UGEL REQUENA</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -5239,6 +5959,16 @@
           <t>160604</t>
         </is>
       </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>UGEL UCAYALI-CONTAMANA</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -5303,6 +6033,16 @@
           <t>160604</t>
         </is>
       </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>UGEL UCAYALI-CONTAMANA</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -5369,6 +6109,16 @@
           <t>160604</t>
         </is>
       </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>UGEL UCAYALI-CONTAMANA</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -5435,6 +6185,16 @@
           <t>200401</t>
         </is>
       </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>UGEL CHULUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -5501,6 +6261,16 @@
           <t>200104</t>
         </is>
       </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -5567,6 +6337,16 @@
           <t>240105</t>
         </is>
       </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>UGEL TUMBES</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -5633,6 +6413,16 @@
           <t>200104</t>
         </is>
       </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -5699,6 +6489,16 @@
           <t>200115</t>
         </is>
       </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -5765,6 +6565,16 @@
           <t>200107</t>
         </is>
       </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -5831,6 +6641,16 @@
           <t>200115</t>
         </is>
       </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -5897,6 +6717,16 @@
           <t>200101</t>
         </is>
       </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -5963,6 +6793,16 @@
           <t>200802</t>
         </is>
       </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>UGEL SECHURA</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -6033,6 +6873,16 @@
           <t>140308</t>
         </is>
       </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -6099,6 +6949,16 @@
           <t>200207</t>
         </is>
       </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>UGEL AYABACA</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -6165,6 +7025,16 @@
           <t>200301</t>
         </is>
       </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>UGEL HUANCABAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -6231,6 +7101,16 @@
           <t>200301</t>
         </is>
       </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>UGEL HUANCABAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -6297,6 +7177,16 @@
           <t>200601</t>
         </is>
       </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>UGEL SULLANA</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -6363,6 +7253,16 @@
           <t>200601</t>
         </is>
       </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>UGEL SULLANA</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -6429,6 +7329,16 @@
           <t>200601</t>
         </is>
       </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>UGEL SULLANA</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -6495,6 +7405,16 @@
           <t>240201</t>
         </is>
       </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>UGEL CONTRALMIRANTE VILLAR</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -6561,6 +7481,16 @@
           <t>240101</t>
         </is>
       </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>UGEL TUMBES</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -6627,6 +7557,16 @@
           <t>240201</t>
         </is>
       </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>UGEL CONTRALMIRANTE VILLAR</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -6693,6 +7633,16 @@
           <t>240106</t>
         </is>
       </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>UGEL TUMBES</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -6759,6 +7709,16 @@
           <t>240101</t>
         </is>
       </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>UGEL TUMBES</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -6825,6 +7785,16 @@
           <t>200109</t>
         </is>
       </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>UGEL LA UNIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -6895,6 +7865,16 @@
           <t>140204</t>
         </is>
       </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>UGEL FERREÑAFE</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -6965,6 +7945,16 @@
           <t>140206</t>
         </is>
       </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>UGEL FERREÑAFE</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -7035,6 +8025,16 @@
           <t>140204</t>
         </is>
       </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>UGEL FERREÑAFE</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -7105,6 +8105,16 @@
           <t>140308</t>
         </is>
       </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -7175,6 +8185,16 @@
           <t>200207</t>
         </is>
       </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>UGEL AYABACA</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -7245,6 +8265,16 @@
           <t>200303</t>
         </is>
       </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>UGEL HUANCABAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -7313,6 +8343,16 @@
           <t>140102</t>
         </is>
       </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>UGEL CHICLAYO</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -7379,6 +8419,16 @@
           <t>200101</t>
         </is>
       </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -7445,6 +8495,16 @@
           <t>200406</t>
         </is>
       </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>UGEL MORROPÓN</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -7511,6 +8571,16 @@
           <t>200802</t>
         </is>
       </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>UGEL SECHURA</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -7577,6 +8647,16 @@
           <t>020110</t>
         </is>
       </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>UGEL HUARAZ</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -7643,6 +8723,16 @@
           <t>020110</t>
         </is>
       </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>UGEL HUARAZ</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -7709,6 +8799,16 @@
           <t>050115</t>
         </is>
       </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -7775,6 +8875,16 @@
           <t>050105</t>
         </is>
       </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -7841,6 +8951,16 @@
           <t>200401</t>
         </is>
       </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>UGEL CHULUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -7907,6 +9027,16 @@
           <t>200404</t>
         </is>
       </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>UGEL CHULUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -7973,6 +9103,16 @@
           <t>200404</t>
         </is>
       </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>UGEL CHULUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -8039,6 +9179,16 @@
           <t>200406</t>
         </is>
       </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>UGEL MORROPÓN</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -8105,6 +9255,16 @@
           <t>200404</t>
         </is>
       </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>UGEL CHULUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -8171,6 +9331,16 @@
           <t>050110</t>
         </is>
       </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -8237,6 +9407,16 @@
           <t>020105</t>
         </is>
       </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>UGEL HUARAZ</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -8303,6 +9483,16 @@
           <t>020105</t>
         </is>
       </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>UGEL HUARAZ</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -8373,6 +9563,16 @@
           <t>200206</t>
         </is>
       </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>UGEL MORROPÓN</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -8439,6 +9639,16 @@
           <t>200406</t>
         </is>
       </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>UGEL MORROPÓN</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -8505,6 +9715,16 @@
           <t>010701</t>
         </is>
       </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>UGEL UTCUBAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -8569,6 +9789,16 @@
           <t>010701</t>
         </is>
       </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>UGEL UTCUBAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -8639,6 +9869,16 @@
           <t>081202</t>
         </is>
       </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>UGEL QUISPICANCHI</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -8709,6 +9949,16 @@
           <t>150106</t>
         </is>
       </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -8779,6 +10029,16 @@
           <t>150117</t>
         </is>
       </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -8849,6 +10109,16 @@
           <t>150123</t>
         </is>
       </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -8919,6 +10189,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -8989,6 +10269,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -9059,6 +10349,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -9129,6 +10429,16 @@
           <t>150601</t>
         </is>
       </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="R131" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -9193,6 +10503,16 @@
           <t>010401</t>
         </is>
       </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="R132" t="inlineStr">
+        <is>
+          <t>UGEL CONDORCANQUI</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -9263,6 +10583,16 @@
           <t>150731</t>
         </is>
       </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="R133" t="inlineStr">
+        <is>
+          <t>UGEL 15 HUAROCHIRÍ</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -9333,6 +10663,16 @@
           <t>150106</t>
         </is>
       </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -9399,6 +10739,16 @@
           <t>010702</t>
         </is>
       </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="R135" t="inlineStr">
+        <is>
+          <t>UGEL UTCUBAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -9463,6 +10813,16 @@
           <t>010702</t>
         </is>
       </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="R136" t="inlineStr">
+        <is>
+          <t>UGEL UTCUBAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -9529,6 +10889,16 @@
           <t>220901</t>
         </is>
       </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="R137" t="inlineStr">
+        <is>
+          <t>UGEL SAN MARTÍN</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -9593,6 +10963,16 @@
           <t>220901</t>
         </is>
       </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="R138" t="inlineStr">
+        <is>
+          <t>UGEL SAN MARTÍN</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -9659,6 +11039,16 @@
           <t>160403</t>
         </is>
       </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>UGEL RAMÓN CASTILLA-CABALLOCOCHA</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -9725,6 +11115,16 @@
           <t>160403</t>
         </is>
       </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>UGEL RAMÓN CASTILLA-CABALLOCOCHA</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -9795,6 +11195,16 @@
           <t>100702</t>
         </is>
       </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>UGEL MARAÑÓN</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -9865,6 +11275,16 @@
           <t>081202</t>
         </is>
       </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>UGEL QUISPICANCHI</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -9935,6 +11355,16 @@
           <t>060801</t>
         </is>
       </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>UGEL JAN</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -10005,6 +11435,16 @@
           <t>081208</t>
         </is>
       </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>UGEL CUSCO</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -10075,6 +11515,16 @@
           <t>060812</t>
         </is>
       </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>UGEL JAN</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -10145,6 +11595,16 @@
           <t>030606</t>
         </is>
       </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>UGEL CHINCHEROS</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -10215,6 +11675,16 @@
           <t>100702</t>
         </is>
       </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>UGEL MARAÑÓN</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -10285,6 +11755,16 @@
           <t>081202</t>
         </is>
       </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>UGEL QUISPICANCHI</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -10355,6 +11835,16 @@
           <t>060906</t>
         </is>
       </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>UGEL SAN IGNACIO</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -10425,6 +11915,16 @@
           <t>010605</t>
         </is>
       </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>UGEL RODRÍGUEZ DE MENDOZA</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -10491,6 +11991,16 @@
           <t>150601</t>
         </is>
       </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -10561,6 +12071,16 @@
           <t>060310</t>
         </is>
       </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>UGEL CELENDÍN</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -10631,6 +12151,16 @@
           <t>150810</t>
         </is>
       </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>UGEL 09 HUAURA</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -10701,6 +12231,16 @@
           <t>010701</t>
         </is>
       </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>UGEL UTCUBAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -10771,6 +12311,16 @@
           <t>030401</t>
         </is>
       </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>UGEL AYMARAES</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -10835,6 +12385,16 @@
           <t>010401</t>
         </is>
       </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>UGEL CONDORCANQUI</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -10899,6 +12459,16 @@
           <t>010401</t>
         </is>
       </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>UGEL CONDORCANQUI</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -10963,6 +12533,16 @@
           <t>010401</t>
         </is>
       </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t>UGEL CONDORCANQUI</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -11027,6 +12607,16 @@
           <t>010401</t>
         </is>
       </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>UGEL CONDORCANQUI</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -11091,6 +12681,16 @@
           <t>010401</t>
         </is>
       </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>UGEL CONDORCANQUI</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -11155,6 +12755,16 @@
           <t>010401</t>
         </is>
       </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>UGEL CONDORCANQUI</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -11219,6 +12829,16 @@
           <t>010401</t>
         </is>
       </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t>UGEL CONDORCANQUI</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -11283,6 +12903,16 @@
           <t>010401</t>
         </is>
       </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="R163" t="inlineStr">
+        <is>
+          <t>UGEL CONDORCANQUI</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -11347,6 +12977,16 @@
           <t>010401</t>
         </is>
       </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="R164" t="inlineStr">
+        <is>
+          <t>UGEL CONDORCANQUI</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -11411,6 +13051,16 @@
           <t>010401</t>
         </is>
       </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="R165" t="inlineStr">
+        <is>
+          <t>UGEL CONDORCANQUI</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -11475,6 +13125,16 @@
           <t>010401</t>
         </is>
       </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t>UGEL CONDORCANQUI</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -11539,6 +13199,16 @@
           <t>010401</t>
         </is>
       </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>UGEL CONDORCANQUI</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -11603,6 +13273,16 @@
           <t>010401</t>
         </is>
       </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="R168" t="inlineStr">
+        <is>
+          <t>UGEL CONDORCANQUI</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -11667,6 +13347,16 @@
           <t>010401</t>
         </is>
       </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>UGEL CONDORCANQUI</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -11731,6 +13421,16 @@
           <t>010401</t>
         </is>
       </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t>UGEL CONDORCANQUI</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -11795,6 +13495,16 @@
           <t>010401</t>
         </is>
       </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>UGEL CONDORCANQUI</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -11859,6 +13569,16 @@
           <t>010401</t>
         </is>
       </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>UGEL CONDORCANQUI</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -11929,6 +13649,16 @@
           <t>070106</t>
         </is>
       </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>UGEL VENTANILLA</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -11999,6 +13729,16 @@
           <t>010701</t>
         </is>
       </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>UGEL UTCUBAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -12065,6 +13805,16 @@
           <t>080902</t>
         </is>
       </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="R175" t="inlineStr">
+        <is>
+          <t>UGEL LA CONVENCIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -12135,6 +13885,16 @@
           <t>130804</t>
         </is>
       </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="R176" t="inlineStr">
+        <is>
+          <t>UGEL PATAZ</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -12205,6 +13965,16 @@
           <t>130804</t>
         </is>
       </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="R177" t="inlineStr">
+        <is>
+          <t>UGEL PATAZ</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -12275,6 +14045,16 @@
           <t>200207</t>
         </is>
       </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t>UGEL AYABACA</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -12345,6 +14125,16 @@
           <t>200207</t>
         </is>
       </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>UGEL AYABACA</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -12415,6 +14205,16 @@
           <t>200403</t>
         </is>
       </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>UGEL MORROPÓN</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -12481,6 +14281,16 @@
           <t>140102</t>
         </is>
       </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>UGEL CHICLAYO</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -12547,6 +14357,16 @@
           <t>140102</t>
         </is>
       </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R182" t="inlineStr">
+        <is>
+          <t>UGEL CHICLAYO</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -12613,6 +14433,16 @@
           <t>140102</t>
         </is>
       </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>UGEL CHICLAYO</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -12679,6 +14509,16 @@
           <t>140102</t>
         </is>
       </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t>UGEL CHICLAYO</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -12745,6 +14585,16 @@
           <t>140119</t>
         </is>
       </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>UGEL CHICLAYO</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -12811,6 +14661,16 @@
           <t>140119</t>
         </is>
       </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>UGEL CHICLAYO</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -12877,6 +14737,16 @@
           <t>140120</t>
         </is>
       </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t>UGEL CHICLAYO</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -12943,6 +14813,16 @@
           <t>140206</t>
         </is>
       </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t>UGEL FERREÑAFE</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -13009,6 +14889,16 @@
           <t>140301</t>
         </is>
       </c>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R189" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -13075,6 +14965,16 @@
           <t>140304</t>
         </is>
       </c>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R190" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -13141,6 +15041,16 @@
           <t>140304</t>
         </is>
       </c>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R191" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -13207,6 +15117,16 @@
           <t>140305</t>
         </is>
       </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R192" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -13273,6 +15193,16 @@
           <t>140305</t>
         </is>
       </c>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R193" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -13339,6 +15269,16 @@
           <t>140305</t>
         </is>
       </c>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R194" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -13405,6 +15345,16 @@
           <t>140306</t>
         </is>
       </c>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R195" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -13471,6 +15421,16 @@
           <t>140306</t>
         </is>
       </c>
+      <c r="Q196" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R196" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -13537,6 +15497,16 @@
           <t>140306</t>
         </is>
       </c>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R197" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -13603,6 +15573,16 @@
           <t>140308</t>
         </is>
       </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -13669,6 +15649,16 @@
           <t>140308</t>
         </is>
       </c>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R199" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -13735,6 +15725,16 @@
           <t>140308</t>
         </is>
       </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R200" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -13801,6 +15801,16 @@
           <t>140308</t>
         </is>
       </c>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R201" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -13867,6 +15877,16 @@
           <t>140308</t>
         </is>
       </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R202" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -13933,6 +15953,16 @@
           <t>140308</t>
         </is>
       </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R203" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -13999,6 +16029,16 @@
           <t>140308</t>
         </is>
       </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R204" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -14065,6 +16105,16 @@
           <t>140309</t>
         </is>
       </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -14131,6 +16181,16 @@
           <t>160301</t>
         </is>
       </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R206" t="inlineStr">
+        <is>
+          <t>UGEL LORETO - NAUTA</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -14195,6 +16255,16 @@
           <t>160301</t>
         </is>
       </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R207" t="inlineStr">
+        <is>
+          <t>UGEL LORETO - NAUTA</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -14261,6 +16331,16 @@
           <t>160301</t>
         </is>
       </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R208" t="inlineStr">
+        <is>
+          <t>UGEL LORETO - NAUTA</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -14325,6 +16405,16 @@
           <t>160301</t>
         </is>
       </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R209" t="inlineStr">
+        <is>
+          <t>UGEL LORETO - NAUTA</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -14391,6 +16481,16 @@
           <t>160504</t>
         </is>
       </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R210" t="inlineStr">
+        <is>
+          <t>UGEL REQUENA</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -14455,6 +16555,16 @@
           <t>160504</t>
         </is>
       </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t>UGEL REQUENA</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -14521,6 +16631,16 @@
           <t>160505</t>
         </is>
       </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t>UGEL REQUENA</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -14585,6 +16705,16 @@
           <t>160505</t>
         </is>
       </c>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R213" t="inlineStr">
+        <is>
+          <t>UGEL REQUENA</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -14651,6 +16781,16 @@
           <t>160505</t>
         </is>
       </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R214" t="inlineStr">
+        <is>
+          <t>UGEL REQUENA</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -14717,6 +16857,16 @@
           <t>140306</t>
         </is>
       </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R215" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -14783,6 +16933,16 @@
           <t>140306</t>
         </is>
       </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R216" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -14849,6 +17009,16 @@
           <t>140308</t>
         </is>
       </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R217" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -14915,6 +17085,16 @@
           <t>140101</t>
         </is>
       </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R218" t="inlineStr">
+        <is>
+          <t>UGEL CHICLAYO</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -14981,6 +17161,16 @@
           <t>140205</t>
         </is>
       </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R219" t="inlineStr">
+        <is>
+          <t>UGEL FERREÑAFE</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -15047,6 +17237,16 @@
           <t>140306</t>
         </is>
       </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R220" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -15113,6 +17313,16 @@
           <t>140306</t>
         </is>
       </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R221" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -15179,6 +17389,16 @@
           <t>140120</t>
         </is>
       </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R222" t="inlineStr">
+        <is>
+          <t>UGEL CHICLAYO</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -15245,6 +17465,16 @@
           <t>140308</t>
         </is>
       </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R223" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -15311,6 +17541,16 @@
           <t>140306</t>
         </is>
       </c>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R224" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -15377,6 +17617,16 @@
           <t>160301</t>
         </is>
       </c>
+      <c r="Q225" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R225" t="inlineStr">
+        <is>
+          <t>UGEL LORETO - NAUTA</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -15441,6 +17691,16 @@
           <t>160301</t>
         </is>
       </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R226" t="inlineStr">
+        <is>
+          <t>UGEL LORETO - NAUTA</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -15507,6 +17767,16 @@
           <t>140306</t>
         </is>
       </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R227" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -15573,6 +17843,16 @@
           <t>160506</t>
         </is>
       </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R228" t="inlineStr">
+        <is>
+          <t>UGEL REQUENA</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -15637,6 +17917,16 @@
           <t>160506</t>
         </is>
       </c>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R229" t="inlineStr">
+        <is>
+          <t>UGEL REQUENA</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -15703,6 +17993,16 @@
           <t>140310</t>
         </is>
       </c>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R230" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -15769,6 +18069,16 @@
           <t>140306</t>
         </is>
       </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R231" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -15835,6 +18145,16 @@
           <t>140308</t>
         </is>
       </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R232" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -15905,6 +18225,16 @@
           <t>150135</t>
         </is>
       </c>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="R233" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -15975,6 +18305,16 @@
           <t>150135</t>
         </is>
       </c>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="R234" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -16045,6 +18385,16 @@
           <t>200206</t>
         </is>
       </c>
+      <c r="Q235" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R235" t="inlineStr">
+        <is>
+          <t>UGEL MORROPÓN</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -16111,6 +18461,16 @@
           <t>140308</t>
         </is>
       </c>
+      <c r="Q236" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R236" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -16177,6 +18537,16 @@
           <t>160106</t>
         </is>
       </c>
+      <c r="Q237" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R237" t="inlineStr">
+        <is>
+          <t>UGEL MAYNAS</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -16241,6 +18611,16 @@
           <t>160106</t>
         </is>
       </c>
+      <c r="Q238" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R238" t="inlineStr">
+        <is>
+          <t>UGEL MAYNAS</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -16307,6 +18687,16 @@
           <t>160706</t>
         </is>
       </c>
+      <c r="Q239" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R239" t="inlineStr">
+        <is>
+          <t>UGEL ALTO AMAZONAS-SAN LORENZO</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -16371,6 +18761,16 @@
           <t>160706</t>
         </is>
       </c>
+      <c r="Q240" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R240" t="inlineStr">
+        <is>
+          <t>UGEL ALTO AMAZONAS-SAN LORENZO</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -16437,6 +18837,16 @@
           <t>140205</t>
         </is>
       </c>
+      <c r="Q241" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R241" t="inlineStr">
+        <is>
+          <t>UGEL FERREÑAFE</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -16503,6 +18913,16 @@
           <t>160704</t>
         </is>
       </c>
+      <c r="Q242" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R242" t="inlineStr">
+        <is>
+          <t>UGEL ALTO AMAZONAS-SAN LORENZO</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -16567,6 +18987,16 @@
           <t>160704</t>
         </is>
       </c>
+      <c r="Q243" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R243" t="inlineStr">
+        <is>
+          <t>UGEL ALTO AMAZONAS-SAN LORENZO</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -16633,6 +19063,16 @@
           <t>140306</t>
         </is>
       </c>
+      <c r="Q244" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R244" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -16699,6 +19139,16 @@
           <t>140308</t>
         </is>
       </c>
+      <c r="Q245" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R245" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -16765,6 +19215,16 @@
           <t>140306</t>
         </is>
       </c>
+      <c r="Q246" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R246" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -16831,6 +19291,16 @@
           <t>160702</t>
         </is>
       </c>
+      <c r="Q247" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R247" t="inlineStr">
+        <is>
+          <t>UGEL ALTO AMAZONAS-SAN LORENZO</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -16895,6 +19365,16 @@
           <t>160702</t>
         </is>
       </c>
+      <c r="Q248" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R248" t="inlineStr">
+        <is>
+          <t>UGEL ALTO AMAZONAS-SAN LORENZO</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -16961,6 +19441,16 @@
           <t>160205</t>
         </is>
       </c>
+      <c r="Q249" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R249" t="inlineStr">
+        <is>
+          <t>UGEL ALTO AMAZONAS-YURIMAGUAS</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -17025,6 +19515,16 @@
           <t>160205</t>
         </is>
       </c>
+      <c r="Q250" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R250" t="inlineStr">
+        <is>
+          <t>UGEL ALTO AMAZONAS-YURIMAGUAS</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -17091,6 +19591,16 @@
           <t>160205</t>
         </is>
       </c>
+      <c r="Q251" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R251" t="inlineStr">
+        <is>
+          <t>UGEL ALTO AMAZONAS-YURIMAGUAS</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -17157,6 +19667,16 @@
           <t>160205</t>
         </is>
       </c>
+      <c r="Q252" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R252" t="inlineStr">
+        <is>
+          <t>UGEL ALTO AMAZONAS-YURIMAGUAS</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -17221,6 +19741,16 @@
           <t>160205</t>
         </is>
       </c>
+      <c r="Q253" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R253" t="inlineStr">
+        <is>
+          <t>UGEL ALTO AMAZONAS-YURIMAGUAS</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -17287,6 +19817,16 @@
           <t>160206</t>
         </is>
       </c>
+      <c r="Q254" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R254" t="inlineStr">
+        <is>
+          <t>UGEL ALTO AMAZONAS-YURIMAGUAS</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -17351,6 +19891,16 @@
           <t>160206</t>
         </is>
       </c>
+      <c r="Q255" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R255" t="inlineStr">
+        <is>
+          <t>UGEL ALTO AMAZONAS-YURIMAGUAS</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -17417,6 +19967,16 @@
           <t>160703</t>
         </is>
       </c>
+      <c r="Q256" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R256" t="inlineStr">
+        <is>
+          <t>UGEL ALTO AMAZONAS-SAN LORENZO</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -17481,6 +20041,16 @@
           <t>160703</t>
         </is>
       </c>
+      <c r="Q257" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R257" t="inlineStr">
+        <is>
+          <t>UGEL ALTO AMAZONAS-SAN LORENZO</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -17547,6 +20117,16 @@
           <t>200108</t>
         </is>
       </c>
+      <c r="Q258" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R258" t="inlineStr">
+        <is>
+          <t>UGEL LA UNIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -17613,6 +20193,16 @@
           <t>200110</t>
         </is>
       </c>
+      <c r="Q259" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R259" t="inlineStr">
+        <is>
+          <t>UGEL LA UNIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -17679,6 +20269,16 @@
           <t>200110</t>
         </is>
       </c>
+      <c r="Q260" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R260" t="inlineStr">
+        <is>
+          <t>UGEL LA UNIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -17745,6 +20345,16 @@
           <t>200110</t>
         </is>
       </c>
+      <c r="Q261" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R261" t="inlineStr">
+        <is>
+          <t>UGEL LA UNIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -17811,6 +20421,16 @@
           <t>200114</t>
         </is>
       </c>
+      <c r="Q262" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R262" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOGRANDE</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -17877,6 +20497,16 @@
           <t>200114</t>
         </is>
       </c>
+      <c r="Q263" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R263" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOGRANDE</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -17943,6 +20573,16 @@
           <t>200114</t>
         </is>
       </c>
+      <c r="Q264" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R264" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOGRANDE</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -18009,6 +20649,16 @@
           <t>200114</t>
         </is>
       </c>
+      <c r="Q265" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R265" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOGRANDE</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -18075,6 +20725,16 @@
           <t>200114</t>
         </is>
       </c>
+      <c r="Q266" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R266" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOGRANDE</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -18141,6 +20801,16 @@
           <t>200114</t>
         </is>
       </c>
+      <c r="Q267" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R267" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOGRANDE</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -18207,6 +20877,16 @@
           <t>200402</t>
         </is>
       </c>
+      <c r="Q268" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R268" t="inlineStr">
+        <is>
+          <t>UGEL MORROPÓN</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -18273,6 +20953,16 @@
           <t>200607</t>
         </is>
       </c>
+      <c r="Q269" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R269" t="inlineStr">
+        <is>
+          <t>UGEL SULLANA</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -18339,6 +21029,16 @@
           <t>220511</t>
         </is>
       </c>
+      <c r="Q270" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="R270" t="inlineStr">
+        <is>
+          <t>UGEL LAMAS</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -18403,6 +21103,16 @@
           <t>220511</t>
         </is>
       </c>
+      <c r="Q271" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="R271" t="inlineStr">
+        <is>
+          <t>UGEL LAMAS</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -18469,6 +21179,16 @@
           <t>220709</t>
         </is>
       </c>
+      <c r="Q272" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="R272" t="inlineStr">
+        <is>
+          <t>UGEL PICOTA</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -18535,6 +21255,16 @@
           <t>221002</t>
         </is>
       </c>
+      <c r="Q273" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="R273" t="inlineStr">
+        <is>
+          <t>UGEL TOCACHE</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -18599,6 +21329,16 @@
           <t>221002</t>
         </is>
       </c>
+      <c r="Q274" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="R274" t="inlineStr">
+        <is>
+          <t>UGEL TOCACHE</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -18665,6 +21405,16 @@
           <t>221002</t>
         </is>
       </c>
+      <c r="Q275" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="R275" t="inlineStr">
+        <is>
+          <t>UGEL TOCACHE</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -18729,6 +21479,16 @@
           <t>221002</t>
         </is>
       </c>
+      <c r="Q276" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="R276" t="inlineStr">
+        <is>
+          <t>UGEL TOCACHE</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -18795,6 +21555,16 @@
           <t>221002</t>
         </is>
       </c>
+      <c r="Q277" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="R277" t="inlineStr">
+        <is>
+          <t>UGEL TOCACHE</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -18861,6 +21631,16 @@
           <t>160705</t>
         </is>
       </c>
+      <c r="Q278" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R278" t="inlineStr">
+        <is>
+          <t>UGEL ALTO AMAZONAS-SAN LORENZO</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -18925,6 +21705,16 @@
           <t>160705</t>
         </is>
       </c>
+      <c r="Q279" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R279" t="inlineStr">
+        <is>
+          <t>UGEL ALTO AMAZONAS-SAN LORENZO</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -18991,6 +21781,16 @@
           <t>160205</t>
         </is>
       </c>
+      <c r="Q280" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R280" t="inlineStr">
+        <is>
+          <t>UGEL ALTO AMAZONAS-YURIMAGUAS</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -19055,6 +21855,16 @@
           <t>160205</t>
         </is>
       </c>
+      <c r="Q281" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R281" t="inlineStr">
+        <is>
+          <t>UGEL ALTO AMAZONAS-YURIMAGUAS</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -19121,6 +21931,16 @@
           <t>200110</t>
         </is>
       </c>
+      <c r="Q282" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R282" t="inlineStr">
+        <is>
+          <t>UGEL LA UNIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -19187,6 +22007,16 @@
           <t>200114</t>
         </is>
       </c>
+      <c r="Q283" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R283" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOGRANDE</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -19251,6 +22081,16 @@
           <t>220708</t>
         </is>
       </c>
+      <c r="Q284" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="R284" t="inlineStr">
+        <is>
+          <t>UGEL PICOTA</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -19317,6 +22157,16 @@
           <t>220709</t>
         </is>
       </c>
+      <c r="Q285" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="R285" t="inlineStr">
+        <is>
+          <t>UGEL PICOTA</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -19381,6 +22231,16 @@
           <t>220709</t>
         </is>
       </c>
+      <c r="Q286" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="R286" t="inlineStr">
+        <is>
+          <t>UGEL PICOTA</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -19447,6 +22307,16 @@
           <t>220708</t>
         </is>
       </c>
+      <c r="Q287" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="R287" t="inlineStr">
+        <is>
+          <t>UGEL PICOTA</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -19511,6 +22381,16 @@
           <t>220708</t>
         </is>
       </c>
+      <c r="Q288" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="R288" t="inlineStr">
+        <is>
+          <t>UGEL PICOTA</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -19577,6 +22457,16 @@
           <t>200104</t>
         </is>
       </c>
+      <c r="Q289" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R289" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -19643,6 +22533,16 @@
           <t>200602</t>
         </is>
       </c>
+      <c r="Q290" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R290" t="inlineStr">
+        <is>
+          <t>UGEL SULLANA</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -19709,6 +22609,16 @@
           <t>200601</t>
         </is>
       </c>
+      <c r="Q291" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R291" t="inlineStr">
+        <is>
+          <t>UGEL SULLANA</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -19779,6 +22689,16 @@
           <t>140107</t>
         </is>
       </c>
+      <c r="Q292" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R292" t="inlineStr">
+        <is>
+          <t>UGEL CHICLAYO</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -19849,6 +22769,16 @@
           <t>140308</t>
         </is>
       </c>
+      <c r="Q293" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R293" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -19915,6 +22845,16 @@
           <t>140101</t>
         </is>
       </c>
+      <c r="Q294" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R294" t="inlineStr">
+        <is>
+          <t>UGEL CHICLAYO</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -19981,6 +22921,16 @@
           <t>150601</t>
         </is>
       </c>
+      <c r="Q295" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="R295" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -20047,6 +22997,16 @@
           <t>200304</t>
         </is>
       </c>
+      <c r="Q296" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R296" t="inlineStr">
+        <is>
+          <t>UGEL HUARMACA</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -20113,6 +23073,16 @@
           <t>200304</t>
         </is>
       </c>
+      <c r="Q297" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R297" t="inlineStr">
+        <is>
+          <t>UGEL HUARMACA</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -20179,6 +23149,16 @@
           <t>200306</t>
         </is>
       </c>
+      <c r="Q298" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R298" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -20245,6 +23225,16 @@
           <t>200603</t>
         </is>
       </c>
+      <c r="Q299" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R299" t="inlineStr">
+        <is>
+          <t>UGEL SULLANA</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -20311,6 +23301,16 @@
           <t>200605</t>
         </is>
       </c>
+      <c r="Q300" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R300" t="inlineStr">
+        <is>
+          <t>UGEL SULLANA</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -20377,6 +23377,16 @@
           <t>200605</t>
         </is>
       </c>
+      <c r="Q301" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R301" t="inlineStr">
+        <is>
+          <t>UGEL SULLANA</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -20443,6 +23453,16 @@
           <t>240101</t>
         </is>
       </c>
+      <c r="Q302" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="R302" t="inlineStr">
+        <is>
+          <t>UGEL TUMBES</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -20509,6 +23529,16 @@
           <t>240101</t>
         </is>
       </c>
+      <c r="Q303" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="R303" t="inlineStr">
+        <is>
+          <t>UGEL TUMBES</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -20575,6 +23605,16 @@
           <t>240104</t>
         </is>
       </c>
+      <c r="Q304" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="R304" t="inlineStr">
+        <is>
+          <t>UGEL TUMBES</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -20641,6 +23681,16 @@
           <t>240104</t>
         </is>
       </c>
+      <c r="Q305" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="R305" t="inlineStr">
+        <is>
+          <t>UGEL TUMBES</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -20707,6 +23757,16 @@
           <t>240105</t>
         </is>
       </c>
+      <c r="Q306" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="R306" t="inlineStr">
+        <is>
+          <t>UGEL TUMBES</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -20773,6 +23833,16 @@
           <t>240106</t>
         </is>
       </c>
+      <c r="Q307" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="R307" t="inlineStr">
+        <is>
+          <t>UGEL TUMBES</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -20839,6 +23909,16 @@
           <t>240106</t>
         </is>
       </c>
+      <c r="Q308" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="R308" t="inlineStr">
+        <is>
+          <t>UGEL TUMBES</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -20905,6 +23985,16 @@
           <t>240301</t>
         </is>
       </c>
+      <c r="Q309" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="R309" t="inlineStr">
+        <is>
+          <t>UGEL ZARUMILLA</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -20971,6 +24061,16 @@
           <t>240304</t>
         </is>
       </c>
+      <c r="Q310" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="R310" t="inlineStr">
+        <is>
+          <t>UGEL ZARUMILLA</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -21037,6 +24137,16 @@
           <t>160206</t>
         </is>
       </c>
+      <c r="Q311" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R311" t="inlineStr">
+        <is>
+          <t>UGEL ALTO AMAZONAS-YURIMAGUAS</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -21101,6 +24211,16 @@
           <t>160206</t>
         </is>
       </c>
+      <c r="Q312" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R312" t="inlineStr">
+        <is>
+          <t>UGEL ALTO AMAZONAS-YURIMAGUAS</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -21167,6 +24287,16 @@
           <t>200104</t>
         </is>
       </c>
+      <c r="Q313" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R313" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -21233,6 +24363,16 @@
           <t>200104</t>
         </is>
       </c>
+      <c r="Q314" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R314" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -21299,6 +24439,16 @@
           <t>160705</t>
         </is>
       </c>
+      <c r="Q315" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R315" t="inlineStr">
+        <is>
+          <t>UGEL ALTO AMAZONAS-SAN LORENZO</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -21363,6 +24513,16 @@
           <t>160705</t>
         </is>
       </c>
+      <c r="Q316" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R316" t="inlineStr">
+        <is>
+          <t>UGEL ALTO AMAZONAS-SAN LORENZO</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -21429,6 +24589,16 @@
           <t>240101</t>
         </is>
       </c>
+      <c r="Q317" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="R317" t="inlineStr">
+        <is>
+          <t>UGEL TUMBES</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -21495,6 +24665,16 @@
           <t>140201</t>
         </is>
       </c>
+      <c r="Q318" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R318" t="inlineStr">
+        <is>
+          <t>UGEL FERREÑAFE</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -21561,6 +24741,16 @@
           <t>240301</t>
         </is>
       </c>
+      <c r="Q319" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="R319" t="inlineStr">
+        <is>
+          <t>UGEL ZARUMILLA</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -21627,6 +24817,16 @@
           <t>160701</t>
         </is>
       </c>
+      <c r="Q320" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R320" t="inlineStr">
+        <is>
+          <t>UGEL ALTO AMAZONAS-SAN LORENZO</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -21691,6 +24891,16 @@
           <t>160701</t>
         </is>
       </c>
+      <c r="Q321" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R321" t="inlineStr">
+        <is>
+          <t>UGEL ALTO AMAZONAS-SAN LORENZO</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -21757,6 +24967,16 @@
           <t>200307</t>
         </is>
       </c>
+      <c r="Q322" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R322" t="inlineStr">
+        <is>
+          <t>UGEL HUANCABAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -21823,6 +25043,16 @@
           <t>200601</t>
         </is>
       </c>
+      <c r="Q323" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R323" t="inlineStr">
+        <is>
+          <t>UGEL SULLANA</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -21889,6 +25119,16 @@
           <t>240303</t>
         </is>
       </c>
+      <c r="Q324" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="R324" t="inlineStr">
+        <is>
+          <t>UGEL ZARUMILLA</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -21955,6 +25195,16 @@
           <t>240101</t>
         </is>
       </c>
+      <c r="Q325" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="R325" t="inlineStr">
+        <is>
+          <t>UGEL TUMBES</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -22021,6 +25271,16 @@
           <t>240101</t>
         </is>
       </c>
+      <c r="Q326" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="R326" t="inlineStr">
+        <is>
+          <t>UGEL TUMBES</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -22087,6 +25347,16 @@
           <t>150601</t>
         </is>
       </c>
+      <c r="Q327" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="R327" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -22157,6 +25427,16 @@
           <t>200407</t>
         </is>
       </c>
+      <c r="Q328" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R328" t="inlineStr">
+        <is>
+          <t>UGEL MORROPÓN</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -22223,6 +25503,16 @@
           <t>140110</t>
         </is>
       </c>
+      <c r="Q329" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R329" t="inlineStr">
+        <is>
+          <t>UGEL CHICLAYO</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -22293,6 +25583,16 @@
           <t>140205</t>
         </is>
       </c>
+      <c r="Q330" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R330" t="inlineStr">
+        <is>
+          <t>UGEL FERREÑAFE</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -22363,6 +25663,16 @@
           <t>140205</t>
         </is>
       </c>
+      <c r="Q331" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R331" t="inlineStr">
+        <is>
+          <t>UGEL FERREÑAFE</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -22433,6 +25743,16 @@
           <t>140118</t>
         </is>
       </c>
+      <c r="Q332" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R332" t="inlineStr">
+        <is>
+          <t>UGEL CHICLAYO</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -22503,6 +25823,16 @@
           <t>140205</t>
         </is>
       </c>
+      <c r="Q333" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R333" t="inlineStr">
+        <is>
+          <t>UGEL FERREÑAFE</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -22567,6 +25897,16 @@
           <t>010401</t>
         </is>
       </c>
+      <c r="Q334" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="R334" t="inlineStr">
+        <is>
+          <t>UGEL CONDORCANQUI</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -22631,6 +25971,16 @@
           <t>010401</t>
         </is>
       </c>
+      <c r="Q335" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="R335" t="inlineStr">
+        <is>
+          <t>UGEL CONDORCANQUI</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -22701,6 +26051,16 @@
           <t>240104</t>
         </is>
       </c>
+      <c r="Q336" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="R336" t="inlineStr">
+        <is>
+          <t>UGEL TUMBES</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -22771,6 +26131,16 @@
           <t>200706</t>
         </is>
       </c>
+      <c r="Q337" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="R337" t="inlineStr">
+        <is>
+          <t>UGEL CONTRALMIRANTE VILLAR</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -22835,6 +26205,16 @@
           <t>010401</t>
         </is>
       </c>
+      <c r="Q338" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="R338" t="inlineStr">
+        <is>
+          <t>UGEL CONDORCANQUI</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -22899,6 +26279,16 @@
           <t>010401</t>
         </is>
       </c>
+      <c r="Q339" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="R339" t="inlineStr">
+        <is>
+          <t>UGEL CONDORCANQUI</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -22963,6 +26353,16 @@
           <t>010401</t>
         </is>
       </c>
+      <c r="Q340" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="R340" t="inlineStr">
+        <is>
+          <t>UGEL CONDORCANQUI</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -23027,6 +26427,16 @@
           <t>010401</t>
         </is>
       </c>
+      <c r="Q341" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="R341" t="inlineStr">
+        <is>
+          <t>UGEL CONDORCANQUI</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -23091,6 +26501,16 @@
           <t>150509</t>
         </is>
       </c>
+      <c r="Q342" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="R342" t="inlineStr">
+        <is>
+          <t>UGEL 08 CAÑETE</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -23161,6 +26581,16 @@
           <t>051001</t>
         </is>
       </c>
+      <c r="Q343" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="R343" t="inlineStr">
+        <is>
+          <t>UGEL VÍCTOR FAJARDO</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -23231,6 +26661,16 @@
           <t>051001</t>
         </is>
       </c>
+      <c r="Q344" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="R344" t="inlineStr">
+        <is>
+          <t>UGEL VÍCTOR FAJARDO</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -23301,6 +26741,16 @@
           <t>051001</t>
         </is>
       </c>
+      <c r="Q345" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="R345" t="inlineStr">
+        <is>
+          <t>UGEL VÍCTOR FAJARDO</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -23367,6 +26817,16 @@
           <t>200111</t>
         </is>
       </c>
+      <c r="Q346" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R346" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOGRANDE</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -23433,6 +26893,16 @@
           <t>200304</t>
         </is>
       </c>
+      <c r="Q347" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R347" t="inlineStr">
+        <is>
+          <t>UGEL HUARMACA</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -23499,6 +26969,16 @@
           <t>200404</t>
         </is>
       </c>
+      <c r="Q348" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R348" t="inlineStr">
+        <is>
+          <t>UGEL CHULUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -23565,6 +27045,16 @@
           <t>200205</t>
         </is>
       </c>
+      <c r="Q349" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R349" t="inlineStr">
+        <is>
+          <t>UGEL AYABACA</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -23631,6 +27121,16 @@
           <t>200805</t>
         </is>
       </c>
+      <c r="Q350" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R350" t="inlineStr">
+        <is>
+          <t>UGEL SECHURA</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -23697,6 +27197,16 @@
           <t>200805</t>
         </is>
       </c>
+      <c r="Q351" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R351" t="inlineStr">
+        <is>
+          <t>UGEL SECHURA</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -23763,6 +27273,16 @@
           <t>200114</t>
         </is>
       </c>
+      <c r="Q352" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R352" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOGRANDE</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -23829,6 +27349,16 @@
           <t>200401</t>
         </is>
       </c>
+      <c r="Q353" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R353" t="inlineStr">
+        <is>
+          <t>UGEL CHULUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -23895,6 +27425,16 @@
           <t>200407</t>
         </is>
       </c>
+      <c r="Q354" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R354" t="inlineStr">
+        <is>
+          <t>UGEL MORROPÓN</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -23961,6 +27501,16 @@
           <t>200801</t>
         </is>
       </c>
+      <c r="Q355" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R355" t="inlineStr">
+        <is>
+          <t>UGEL SECHURA</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -24027,6 +27577,16 @@
           <t>200401</t>
         </is>
       </c>
+      <c r="Q356" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R356" t="inlineStr">
+        <is>
+          <t>UGEL CHULUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -24097,6 +27657,16 @@
           <t>140102</t>
         </is>
       </c>
+      <c r="Q357" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R357" t="inlineStr">
+        <is>
+          <t>UGEL CHICLAYO</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -24167,6 +27737,16 @@
           <t>200115</t>
         </is>
       </c>
+      <c r="Q358" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="R358" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -24233,6 +27813,16 @@
           <t>010521</t>
         </is>
       </c>
+      <c r="Q359" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="R359" t="inlineStr">
+        <is>
+          <t>UGEL LUYA</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -24299,6 +27889,16 @@
           <t>022008</t>
         </is>
       </c>
+      <c r="Q360" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="R360" t="inlineStr">
+        <is>
+          <t>UGEL YUNGAY</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -24365,6 +27965,16 @@
           <t>050706</t>
         </is>
       </c>
+      <c r="Q361" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="R361" t="inlineStr">
+        <is>
+          <t>UGEL PARINACOCHAS</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -24431,6 +28041,16 @@
           <t>060104</t>
         </is>
       </c>
+      <c r="Q362" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="R362" t="inlineStr">
+        <is>
+          <t>UGEL CAJAMARCA</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -24497,6 +28117,16 @@
           <t>060801</t>
         </is>
       </c>
+      <c r="Q363" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="R363" t="inlineStr">
+        <is>
+          <t>UGEL JAN</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -24563,6 +28193,16 @@
           <t>060801</t>
         </is>
       </c>
+      <c r="Q364" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="R364" t="inlineStr">
+        <is>
+          <t>UGEL JAN</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -24629,6 +28269,16 @@
           <t>060801</t>
         </is>
       </c>
+      <c r="Q365" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="R365" t="inlineStr">
+        <is>
+          <t>UGEL JAN</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -24695,6 +28345,16 @@
           <t>060806</t>
         </is>
       </c>
+      <c r="Q366" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="R366" t="inlineStr">
+        <is>
+          <t>UGEL JAN</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -24761,6 +28421,16 @@
           <t>061305</t>
         </is>
       </c>
+      <c r="Q367" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="R367" t="inlineStr">
+        <is>
+          <t>UGEL SANTA CRUZ</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -24827,6 +28497,16 @@
           <t>100102</t>
         </is>
       </c>
+      <c r="Q368" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="R368" t="inlineStr">
+        <is>
+          <t>UGEL HUÁNUCO</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -24893,6 +28573,16 @@
           <t>110101</t>
         </is>
       </c>
+      <c r="Q369" t="inlineStr">
+        <is>
+          <t>DRE ICA</t>
+        </is>
+      </c>
+      <c r="R369" t="inlineStr">
+        <is>
+          <t>UGEL ICA</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -24959,6 +28649,16 @@
           <t>110101</t>
         </is>
       </c>
+      <c r="Q370" t="inlineStr">
+        <is>
+          <t>DRE ICA</t>
+        </is>
+      </c>
+      <c r="R370" t="inlineStr">
+        <is>
+          <t>UGEL ICA</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -25025,6 +28725,16 @@
           <t>110108</t>
         </is>
       </c>
+      <c r="Q371" t="inlineStr">
+        <is>
+          <t>DRE ICA</t>
+        </is>
+      </c>
+      <c r="R371" t="inlineStr">
+        <is>
+          <t>UGEL ICA</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -25091,6 +28801,16 @@
           <t>110302</t>
         </is>
       </c>
+      <c r="Q372" t="inlineStr">
+        <is>
+          <t>DRE ICA</t>
+        </is>
+      </c>
+      <c r="R372" t="inlineStr">
+        <is>
+          <t>UGEL PALPA</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -25157,6 +28877,16 @@
           <t>110302</t>
         </is>
       </c>
+      <c r="Q373" t="inlineStr">
+        <is>
+          <t>DRE ICA</t>
+        </is>
+      </c>
+      <c r="R373" t="inlineStr">
+        <is>
+          <t>UGEL PALPA</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -25223,6 +28953,16 @@
           <t>110305</t>
         </is>
       </c>
+      <c r="Q374" t="inlineStr">
+        <is>
+          <t>DRE ICA</t>
+        </is>
+      </c>
+      <c r="R374" t="inlineStr">
+        <is>
+          <t>UGEL NASCA</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -25289,6 +29029,16 @@
           <t>110501</t>
         </is>
       </c>
+      <c r="Q375" t="inlineStr">
+        <is>
+          <t>DRE ICA</t>
+        </is>
+      </c>
+      <c r="R375" t="inlineStr">
+        <is>
+          <t>UGEL PISCO</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -25355,6 +29105,16 @@
           <t>120301</t>
         </is>
       </c>
+      <c r="Q376" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="R376" t="inlineStr">
+        <is>
+          <t>UGEL CHANCHAMAYO</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -25419,6 +29179,16 @@
       <c r="P377" t="inlineStr">
         <is>
           <t>120302</t>
+        </is>
+      </c>
+      <c r="Q377" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="R377" t="inlineStr">
+        <is>
+          <t>UGEL CHANCHAMAYO</t>
         </is>
       </c>
     </row>
@@ -25467,6 +29237,8 @@
       <c r="N378" t="inlineStr"/>
       <c r="O378" t="inlineStr"/>
       <c r="P378" t="inlineStr"/>
+      <c r="Q378" t="inlineStr"/>
+      <c r="R378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -25533,6 +29305,16 @@
           <t>120607</t>
         </is>
       </c>
+      <c r="Q379" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="R379" t="inlineStr">
+        <is>
+          <t>UGEL SATIPO</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -25599,6 +29381,16 @@
           <t>120706</t>
         </is>
       </c>
+      <c r="Q380" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="R380" t="inlineStr">
+        <is>
+          <t>UGEL TARMA</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -25665,6 +29457,16 @@
           <t>130303</t>
         </is>
       </c>
+      <c r="Q381" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="R381" t="inlineStr">
+        <is>
+          <t>UGEL SÁNCHEZ CARRIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -25731,6 +29533,16 @@
           <t>130303</t>
         </is>
       </c>
+      <c r="Q382" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="R382" t="inlineStr">
+        <is>
+          <t>UGEL SÁNCHEZ CARRIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -25797,6 +29609,16 @@
           <t>131104</t>
         </is>
       </c>
+      <c r="Q383" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="R383" t="inlineStr">
+        <is>
+          <t>UGEL GRAN CHIMÚ</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -25863,6 +29685,16 @@
           <t>140119</t>
         </is>
       </c>
+      <c r="Q384" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R384" t="inlineStr">
+        <is>
+          <t>UGEL CHICLAYO</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -25929,6 +29761,16 @@
           <t>140120</t>
         </is>
       </c>
+      <c r="Q385" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R385" t="inlineStr">
+        <is>
+          <t>UGEL CHICLAYO</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -25995,6 +29837,16 @@
           <t>140301</t>
         </is>
       </c>
+      <c r="Q386" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R386" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -26061,6 +29913,16 @@
           <t>140306</t>
         </is>
       </c>
+      <c r="Q387" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R387" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -26127,6 +29989,16 @@
           <t>140307</t>
         </is>
       </c>
+      <c r="Q388" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R388" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -26193,6 +30065,16 @@
           <t>140308</t>
         </is>
       </c>
+      <c r="Q389" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R389" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -26259,6 +30141,16 @@
           <t>140311</t>
         </is>
       </c>
+      <c r="Q390" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R390" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -26325,6 +30217,16 @@
           <t>140312</t>
         </is>
       </c>
+      <c r="Q391" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R391" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -26391,6 +30293,16 @@
           <t>140312</t>
         </is>
       </c>
+      <c r="Q392" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R392" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -26457,6 +30369,16 @@
           <t>140312</t>
         </is>
       </c>
+      <c r="Q393" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R393" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -26523,6 +30445,16 @@
           <t>150106</t>
         </is>
       </c>
+      <c r="Q394" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="R394" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -26589,6 +30521,16 @@
           <t>150510</t>
         </is>
       </c>
+      <c r="Q395" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="R395" t="inlineStr">
+        <is>
+          <t>UGEL 08 CAÑETE</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -26655,6 +30597,16 @@
           <t>150709</t>
         </is>
       </c>
+      <c r="Q396" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="R396" t="inlineStr">
+        <is>
+          <t>UGEL 15 HUAROCHIRÍ</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -26721,6 +30673,16 @@
           <t>160201</t>
         </is>
       </c>
+      <c r="Q397" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="R397" t="inlineStr">
+        <is>
+          <t>UGEL ALTO AMAZONAS-YURIMAGUAS</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -26787,6 +30749,16 @@
           <t>210303</t>
         </is>
       </c>
+      <c r="Q398" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="R398" t="inlineStr">
+        <is>
+          <t>UGEL CARABAYA</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -26853,6 +30825,16 @@
           <t>210309</t>
         </is>
       </c>
+      <c r="Q399" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="R399" t="inlineStr">
+        <is>
+          <t>UGEL CARABAYA</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -26919,6 +30901,16 @@
           <t>211207</t>
         </is>
       </c>
+      <c r="Q400" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="R400" t="inlineStr">
+        <is>
+          <t>UGEL SANDIA</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -26985,6 +30977,16 @@
           <t>211207</t>
         </is>
       </c>
+      <c r="Q401" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="R401" t="inlineStr">
+        <is>
+          <t>UGEL SANDIA</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -27051,6 +31053,16 @@
           <t>240101</t>
         </is>
       </c>
+      <c r="Q402" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="R402" t="inlineStr">
+        <is>
+          <t>UGEL TUMBES</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -27117,6 +31129,16 @@
           <t>240106</t>
         </is>
       </c>
+      <c r="Q403" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="R403" t="inlineStr">
+        <is>
+          <t>UGEL TUMBES</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -27183,6 +31205,16 @@
           <t>240106</t>
         </is>
       </c>
+      <c r="Q404" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="R404" t="inlineStr">
+        <is>
+          <t>UGEL TUMBES</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -27249,6 +31281,16 @@
           <t>240106</t>
         </is>
       </c>
+      <c r="Q405" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="R405" t="inlineStr">
+        <is>
+          <t>UGEL TUMBES</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -27315,6 +31357,16 @@
           <t>240301</t>
         </is>
       </c>
+      <c r="Q406" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="R406" t="inlineStr">
+        <is>
+          <t>UGEL ZARUMILLA</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
@@ -27381,6 +31433,16 @@
           <t>240304</t>
         </is>
       </c>
+      <c r="Q407" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="R407" t="inlineStr">
+        <is>
+          <t>UGEL ZARUMILLA</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -27447,6 +31509,16 @@
           <t>250104</t>
         </is>
       </c>
+      <c r="Q408" t="inlineStr">
+        <is>
+          <t>DRE UCAYALI</t>
+        </is>
+      </c>
+      <c r="R408" t="inlineStr">
+        <is>
+          <t>UGEL CORONEL PORTILLO</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
@@ -27513,6 +31585,16 @@
           <t>250104</t>
         </is>
       </c>
+      <c r="Q409" t="inlineStr">
+        <is>
+          <t>DRE UCAYALI</t>
+        </is>
+      </c>
+      <c r="R409" t="inlineStr">
+        <is>
+          <t>UGEL CORONEL PORTILLO</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -27579,6 +31661,16 @@
           <t>250303</t>
         </is>
       </c>
+      <c r="Q410" t="inlineStr">
+        <is>
+          <t>DRE UCAYALI</t>
+        </is>
+      </c>
+      <c r="R410" t="inlineStr">
+        <is>
+          <t>UGEL PADRE ABAD</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -27645,6 +31737,16 @@
           <t>050407</t>
         </is>
       </c>
+      <c r="Q411" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="R411" t="inlineStr">
+        <is>
+          <t>UGEL HUANTA</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -27711,6 +31813,16 @@
           <t>061112</t>
         </is>
       </c>
+      <c r="Q412" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="R412" t="inlineStr">
+        <is>
+          <t>UGEL SAN MIGUEL</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -27777,6 +31889,16 @@
           <t>110109</t>
         </is>
       </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>DRE ICA</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr">
+        <is>
+          <t>UGEL ICA</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -27843,6 +31965,16 @@
           <t>140306</t>
         </is>
       </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -27909,6 +32041,16 @@
           <t>211210</t>
         </is>
       </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr">
+        <is>
+          <t>UGEL SANDIA</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -27975,6 +32117,16 @@
           <t>211210</t>
         </is>
       </c>
+      <c r="Q416" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="R416" t="inlineStr">
+        <is>
+          <t>UGEL SANDIA</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
@@ -28041,6 +32193,16 @@
           <t>140308</t>
         </is>
       </c>
+      <c r="Q417" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R417" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -28105,6 +32267,16 @@
       <c r="P418" t="inlineStr">
         <is>
           <t>140308</t>
+        </is>
+      </c>
+      <c r="Q418" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="R418" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
     </row>

--- a/output/bases_limpias/Grupo_03_MODULOS/df_ugme_modulares.xlsx
+++ b/output/bases_limpias/Grupo_03_MODULOS/df_ugme_modulares.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R418"/>
+  <dimension ref="A1:S418"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,6 +507,11 @@
           <t>ugel</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>fuente</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -583,6 +588,11 @@
           <t>UGEL HUARAZ</t>
         </is>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -659,6 +669,11 @@
           <t>UGEL YUNGAY</t>
         </is>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -735,6 +750,11 @@
           <t>UGEL YUNGAY</t>
         </is>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -811,6 +831,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -887,6 +912,11 @@
           <t>UGEL PARINACOCHAS</t>
         </is>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -963,6 +993,11 @@
           <t>UGEL JULCÁN</t>
         </is>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1039,6 +1074,11 @@
           <t>UGEL JULCÁN</t>
         </is>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1115,6 +1155,11 @@
           <t>UGEL OTUZCO</t>
         </is>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1191,6 +1236,11 @@
           <t>UGEL SÁNCHEZ CARRIÓN</t>
         </is>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1271,6 +1321,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1347,6 +1402,11 @@
           <t>UGEL ALTO AMAZONAS-SAN LORENZO</t>
         </is>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1421,6 +1481,11 @@
           <t>UGEL ALTO AMAZONAS-SAN LORENZO</t>
         </is>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1497,6 +1562,11 @@
           <t>UGEL REQUENA</t>
         </is>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1571,6 +1641,11 @@
           <t>UGEL REQUENA</t>
         </is>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1647,6 +1722,11 @@
           <t>UGEL REQUENA</t>
         </is>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1721,6 +1801,11 @@
           <t>UGEL REQUENA</t>
         </is>
       </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1797,6 +1882,11 @@
           <t>UGEL UCAYALI-CONTAMANA</t>
         </is>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1871,6 +1961,11 @@
           <t>UGEL UCAYALI-CONTAMANA</t>
         </is>
       </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1947,6 +2042,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2023,6 +2123,11 @@
           <t>UGEL LA UNIÓN</t>
         </is>
       </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2099,6 +2204,11 @@
           <t>UGEL AYABACA</t>
         </is>
       </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2175,6 +2285,11 @@
           <t>UGEL AYABACA</t>
         </is>
       </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2251,6 +2366,11 @@
           <t>UGEL AYABACA</t>
         </is>
       </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2327,6 +2447,11 @@
           <t>UGEL AYABACA</t>
         </is>
       </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2403,6 +2528,11 @@
           <t>UGEL AYABACA</t>
         </is>
       </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2479,6 +2609,11 @@
           <t>UGEL AYABACA</t>
         </is>
       </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2555,6 +2690,11 @@
           <t>UGEL AYABACA</t>
         </is>
       </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2631,6 +2771,11 @@
           <t>UGEL HUANCABAMBA</t>
         </is>
       </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2707,6 +2852,11 @@
           <t>UGEL HUANCABAMBA</t>
         </is>
       </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2783,6 +2933,11 @@
           <t>UGEL HUANCABAMBA</t>
         </is>
       </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2859,6 +3014,11 @@
           <t>UGEL HUARMACA</t>
         </is>
       </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2935,6 +3095,11 @@
           <t>UGEL HUARMACA</t>
         </is>
       </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3011,6 +3176,11 @@
           <t>UGEL HUARMACA</t>
         </is>
       </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3087,6 +3257,11 @@
           <t>UGEL HUARMACA</t>
         </is>
       </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -3163,6 +3338,11 @@
           <t>UGEL HUARMACA</t>
         </is>
       </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -3239,6 +3419,11 @@
           <t>UGEL HUARMACA</t>
         </is>
       </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3315,6 +3500,11 @@
           <t>UGEL HUARMACA</t>
         </is>
       </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3391,6 +3581,11 @@
           <t>UGEL HUARMACA</t>
         </is>
       </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3467,6 +3662,11 @@
           <t>UGEL HUARMACA</t>
         </is>
       </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3543,6 +3743,11 @@
           <t>UGEL CHULUCANAS</t>
         </is>
       </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -3619,6 +3824,11 @@
           <t>UGEL CHULUCANAS</t>
         </is>
       </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -3695,6 +3905,11 @@
           <t>UGEL CHULUCANAS</t>
         </is>
       </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -3771,6 +3986,11 @@
           <t>UGEL CHULUCANAS</t>
         </is>
       </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3847,6 +4067,11 @@
           <t>UGEL CHULUCANAS</t>
         </is>
       </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3923,6 +4148,11 @@
           <t>UGEL CHULUCANAS</t>
         </is>
       </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3999,6 +4229,11 @@
           <t>UGEL MORROPÓN</t>
         </is>
       </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -4075,6 +4310,11 @@
           <t>UGEL MORROPÓN</t>
         </is>
       </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -4151,6 +4391,11 @@
           <t>UGEL SULLANA</t>
         </is>
       </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -4227,6 +4472,11 @@
           <t>UGEL SULLANA</t>
         </is>
       </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -4303,6 +4553,11 @@
           <t>UGEL SULLANA</t>
         </is>
       </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -4379,6 +4634,11 @@
           <t>UGEL CONTRALMIRANTE VILLAR</t>
         </is>
       </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -4455,6 +4715,11 @@
           <t>UGEL SECHURA</t>
         </is>
       </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -4531,6 +4796,11 @@
           <t>UGEL TUMBES</t>
         </is>
       </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -4607,6 +4877,11 @@
           <t>UGEL TUMBES</t>
         </is>
       </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -4683,6 +4958,11 @@
           <t>UGEL TUMBES</t>
         </is>
       </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -4759,6 +5039,11 @@
           <t>UGEL TUMBES</t>
         </is>
       </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -4835,6 +5120,11 @@
           <t>UGEL TUMBES</t>
         </is>
       </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -4911,6 +5201,11 @@
           <t>UGEL TUMBES</t>
         </is>
       </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -4987,6 +5282,11 @@
           <t>UGEL CONTRALMIRANTE VILLAR</t>
         </is>
       </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -5061,6 +5361,11 @@
       <c r="R61" t="inlineStr">
         <is>
           <t>UGEL TUMBES</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>UGME</t>
         </is>
       </c>
     </row>
@@ -5139,6 +5444,11 @@
           <t>UGEL AYABACA</t>
         </is>
       </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -5215,6 +5525,11 @@
           <t>UGEL AYABACA</t>
         </is>
       </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -5291,6 +5606,11 @@
           <t>UGEL TAMBOGRANDE</t>
         </is>
       </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -5367,6 +5687,11 @@
           <t>UGEL ALTO AMAZONAS-SAN LORENZO</t>
         </is>
       </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -5441,6 +5766,11 @@
           <t>UGEL ALTO AMAZONAS-SAN LORENZO</t>
         </is>
       </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -5517,6 +5847,11 @@
           <t>UGEL ALTO AMAZONAS-SAN LORENZO</t>
         </is>
       </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -5591,6 +5926,11 @@
           <t>UGEL ALTO AMAZONAS-SAN LORENZO</t>
         </is>
       </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -5667,6 +6007,11 @@
           <t>UGEL SÁNCHEZ CARRIÓN</t>
         </is>
       </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -5743,6 +6088,11 @@
           <t>UGEL CONTRALMIRANTE VILLAR</t>
         </is>
       </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -5819,6 +6169,11 @@
           <t>UGEL REQUENA</t>
         </is>
       </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -5893,6 +6248,11 @@
           <t>UGEL REQUENA</t>
         </is>
       </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -5969,6 +6329,11 @@
           <t>UGEL UCAYALI-CONTAMANA</t>
         </is>
       </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -6043,6 +6408,11 @@
           <t>UGEL UCAYALI-CONTAMANA</t>
         </is>
       </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -6119,6 +6489,11 @@
           <t>UGEL UCAYALI-CONTAMANA</t>
         </is>
       </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -6195,6 +6570,11 @@
           <t>UGEL CHULUCANAS</t>
         </is>
       </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -6271,6 +6651,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -6347,6 +6732,11 @@
           <t>UGEL TUMBES</t>
         </is>
       </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -6423,6 +6813,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -6499,6 +6894,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -6575,6 +6975,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -6651,6 +7056,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -6727,6 +7137,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -6803,6 +7218,11 @@
           <t>UGEL SECHURA</t>
         </is>
       </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -6883,6 +7303,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -6959,6 +7384,11 @@
           <t>UGEL AYABACA</t>
         </is>
       </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -7035,6 +7465,11 @@
           <t>UGEL HUANCABAMBA</t>
         </is>
       </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -7111,6 +7546,11 @@
           <t>UGEL HUANCABAMBA</t>
         </is>
       </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -7187,6 +7627,11 @@
           <t>UGEL SULLANA</t>
         </is>
       </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -7263,6 +7708,11 @@
           <t>UGEL SULLANA</t>
         </is>
       </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -7339,6 +7789,11 @@
           <t>UGEL SULLANA</t>
         </is>
       </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -7415,6 +7870,11 @@
           <t>UGEL CONTRALMIRANTE VILLAR</t>
         </is>
       </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -7491,6 +7951,11 @@
           <t>UGEL TUMBES</t>
         </is>
       </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -7567,6 +8032,11 @@
           <t>UGEL CONTRALMIRANTE VILLAR</t>
         </is>
       </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -7643,6 +8113,11 @@
           <t>UGEL TUMBES</t>
         </is>
       </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -7719,6 +8194,11 @@
           <t>UGEL TUMBES</t>
         </is>
       </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -7795,6 +8275,11 @@
           <t>UGEL LA UNIÓN</t>
         </is>
       </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -7875,6 +8360,11 @@
           <t>UGEL FERREÑAFE</t>
         </is>
       </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -7955,6 +8445,11 @@
           <t>UGEL FERREÑAFE</t>
         </is>
       </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -8035,6 +8530,11 @@
           <t>UGEL FERREÑAFE</t>
         </is>
       </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -8115,6 +8615,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -8195,6 +8700,11 @@
           <t>UGEL AYABACA</t>
         </is>
       </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -8275,6 +8785,11 @@
           <t>UGEL HUANCABAMBA</t>
         </is>
       </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -8353,6 +8868,11 @@
           <t>UGEL CHICLAYO</t>
         </is>
       </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -8429,6 +8949,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -8505,6 +9030,11 @@
           <t>UGEL MORROPÓN</t>
         </is>
       </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -8581,6 +9111,11 @@
           <t>UGEL SECHURA</t>
         </is>
       </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -8657,6 +9192,11 @@
           <t>UGEL HUARAZ</t>
         </is>
       </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -8733,6 +9273,11 @@
           <t>UGEL HUARAZ</t>
         </is>
       </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -8809,6 +9354,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -8885,6 +9435,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -8961,6 +9516,11 @@
           <t>UGEL CHULUCANAS</t>
         </is>
       </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -9037,6 +9597,11 @@
           <t>UGEL CHULUCANAS</t>
         </is>
       </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -9113,6 +9678,11 @@
           <t>UGEL CHULUCANAS</t>
         </is>
       </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -9189,6 +9759,11 @@
           <t>UGEL MORROPÓN</t>
         </is>
       </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -9265,6 +9840,11 @@
           <t>UGEL CHULUCANAS</t>
         </is>
       </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -9341,6 +9921,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -9417,6 +10002,11 @@
           <t>UGEL HUARAZ</t>
         </is>
       </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -9493,6 +10083,11 @@
           <t>UGEL HUARAZ</t>
         </is>
       </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -9573,6 +10168,11 @@
           <t>UGEL MORROPÓN</t>
         </is>
       </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -9649,6 +10249,11 @@
           <t>UGEL MORROPÓN</t>
         </is>
       </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -9725,6 +10330,11 @@
           <t>UGEL UTCUBAMBA</t>
         </is>
       </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -9799,6 +10409,11 @@
           <t>UGEL UTCUBAMBA</t>
         </is>
       </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -9879,6 +10494,11 @@
           <t>UGEL QUISPICANCHI</t>
         </is>
       </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -9959,6 +10579,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -10039,6 +10664,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -10119,6 +10749,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -10199,6 +10834,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -10279,6 +10919,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -10359,6 +11004,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -10439,6 +11089,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -10513,6 +11168,11 @@
           <t>UGEL CONDORCANQUI</t>
         </is>
       </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -10593,6 +11253,11 @@
           <t>UGEL 15 HUAROCHIRÍ</t>
         </is>
       </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -10673,6 +11338,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -10749,6 +11419,11 @@
           <t>UGEL UTCUBAMBA</t>
         </is>
       </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -10823,6 +11498,11 @@
           <t>UGEL UTCUBAMBA</t>
         </is>
       </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -10899,6 +11579,11 @@
           <t>UGEL SAN MARTÍN</t>
         </is>
       </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -10973,6 +11658,11 @@
           <t>UGEL SAN MARTÍN</t>
         </is>
       </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -11049,6 +11739,11 @@
           <t>UGEL RAMÓN CASTILLA-CABALLOCOCHA</t>
         </is>
       </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -11125,6 +11820,11 @@
           <t>UGEL RAMÓN CASTILLA-CABALLOCOCHA</t>
         </is>
       </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -11205,6 +11905,11 @@
           <t>UGEL MARAÑÓN</t>
         </is>
       </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -11285,6 +11990,11 @@
           <t>UGEL QUISPICANCHI</t>
         </is>
       </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -11365,6 +12075,11 @@
           <t>UGEL JAN</t>
         </is>
       </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -11445,6 +12160,11 @@
           <t>UGEL CUSCO</t>
         </is>
       </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -11525,6 +12245,11 @@
           <t>UGEL JAN</t>
         </is>
       </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -11605,6 +12330,11 @@
           <t>UGEL CHINCHEROS</t>
         </is>
       </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -11685,6 +12415,11 @@
           <t>UGEL MARAÑÓN</t>
         </is>
       </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -11765,6 +12500,11 @@
           <t>UGEL QUISPICANCHI</t>
         </is>
       </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -11845,6 +12585,11 @@
           <t>UGEL SAN IGNACIO</t>
         </is>
       </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -11925,6 +12670,11 @@
           <t>UGEL RODRÍGUEZ DE MENDOZA</t>
         </is>
       </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -12001,6 +12751,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -12081,6 +12836,11 @@
           <t>UGEL CELENDÍN</t>
         </is>
       </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -12161,6 +12921,11 @@
           <t>UGEL 09 HUAURA</t>
         </is>
       </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -12241,6 +13006,11 @@
           <t>UGEL UTCUBAMBA</t>
         </is>
       </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -12321,6 +13091,11 @@
           <t>UGEL AYMARAES</t>
         </is>
       </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -12395,6 +13170,11 @@
           <t>UGEL CONDORCANQUI</t>
         </is>
       </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -12469,6 +13249,11 @@
           <t>UGEL CONDORCANQUI</t>
         </is>
       </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -12543,6 +13328,11 @@
           <t>UGEL CONDORCANQUI</t>
         </is>
       </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -12617,6 +13407,11 @@
           <t>UGEL CONDORCANQUI</t>
         </is>
       </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -12691,6 +13486,11 @@
           <t>UGEL CONDORCANQUI</t>
         </is>
       </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -12765,6 +13565,11 @@
           <t>UGEL CONDORCANQUI</t>
         </is>
       </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -12839,6 +13644,11 @@
           <t>UGEL CONDORCANQUI</t>
         </is>
       </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -12913,6 +13723,11 @@
           <t>UGEL CONDORCANQUI</t>
         </is>
       </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -12987,6 +13802,11 @@
           <t>UGEL CONDORCANQUI</t>
         </is>
       </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -13061,6 +13881,11 @@
           <t>UGEL CONDORCANQUI</t>
         </is>
       </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -13135,6 +13960,11 @@
           <t>UGEL CONDORCANQUI</t>
         </is>
       </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -13209,6 +14039,11 @@
           <t>UGEL CONDORCANQUI</t>
         </is>
       </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -13283,6 +14118,11 @@
           <t>UGEL CONDORCANQUI</t>
         </is>
       </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -13357,6 +14197,11 @@
           <t>UGEL CONDORCANQUI</t>
         </is>
       </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -13431,6 +14276,11 @@
           <t>UGEL CONDORCANQUI</t>
         </is>
       </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -13505,6 +14355,11 @@
           <t>UGEL CONDORCANQUI</t>
         </is>
       </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -13579,6 +14434,11 @@
           <t>UGEL CONDORCANQUI</t>
         </is>
       </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -13659,6 +14519,11 @@
           <t>UGEL VENTANILLA</t>
         </is>
       </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -13739,6 +14604,11 @@
           <t>UGEL UTCUBAMBA</t>
         </is>
       </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -13815,6 +14685,11 @@
           <t>UGEL LA CONVENCIÓN</t>
         </is>
       </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -13895,6 +14770,11 @@
           <t>UGEL PATAZ</t>
         </is>
       </c>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -13975,6 +14855,11 @@
           <t>UGEL PATAZ</t>
         </is>
       </c>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -14055,6 +14940,11 @@
           <t>UGEL AYABACA</t>
         </is>
       </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -14135,6 +15025,11 @@
           <t>UGEL AYABACA</t>
         </is>
       </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -14215,6 +15110,11 @@
           <t>UGEL MORROPÓN</t>
         </is>
       </c>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -14291,6 +15191,11 @@
           <t>UGEL CHICLAYO</t>
         </is>
       </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -14367,6 +15272,11 @@
           <t>UGEL CHICLAYO</t>
         </is>
       </c>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -14443,6 +15353,11 @@
           <t>UGEL CHICLAYO</t>
         </is>
       </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -14519,6 +15434,11 @@
           <t>UGEL CHICLAYO</t>
         </is>
       </c>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -14595,6 +15515,11 @@
           <t>UGEL CHICLAYO</t>
         </is>
       </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -14671,6 +15596,11 @@
           <t>UGEL CHICLAYO</t>
         </is>
       </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -14747,6 +15677,11 @@
           <t>UGEL CHICLAYO</t>
         </is>
       </c>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -14823,6 +15758,11 @@
           <t>UGEL FERREÑAFE</t>
         </is>
       </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -14899,6 +15839,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -14975,6 +15920,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -15051,6 +16001,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -15127,6 +16082,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -15203,6 +16163,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -15279,6 +16244,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -15355,6 +16325,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -15431,6 +16406,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -15507,6 +16487,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -15583,6 +16568,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -15659,6 +16649,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -15735,6 +16730,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -15811,6 +16811,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -15887,6 +16892,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -15963,6 +16973,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -16039,6 +17054,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -16115,6 +17135,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -16191,6 +17216,11 @@
           <t>UGEL LORETO - NAUTA</t>
         </is>
       </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -16265,6 +17295,11 @@
           <t>UGEL LORETO - NAUTA</t>
         </is>
       </c>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -16341,6 +17376,11 @@
           <t>UGEL LORETO - NAUTA</t>
         </is>
       </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -16415,6 +17455,11 @@
           <t>UGEL LORETO - NAUTA</t>
         </is>
       </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -16491,6 +17536,11 @@
           <t>UGEL REQUENA</t>
         </is>
       </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -16565,6 +17615,11 @@
           <t>UGEL REQUENA</t>
         </is>
       </c>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -16641,6 +17696,11 @@
           <t>UGEL REQUENA</t>
         </is>
       </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -16715,6 +17775,11 @@
           <t>UGEL REQUENA</t>
         </is>
       </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -16791,6 +17856,11 @@
           <t>UGEL REQUENA</t>
         </is>
       </c>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -16867,6 +17937,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -16943,6 +18018,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -17019,6 +18099,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -17095,6 +18180,11 @@
           <t>UGEL CHICLAYO</t>
         </is>
       </c>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -17171,6 +18261,11 @@
           <t>UGEL FERREÑAFE</t>
         </is>
       </c>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -17247,6 +18342,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -17323,6 +18423,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -17399,6 +18504,11 @@
           <t>UGEL CHICLAYO</t>
         </is>
       </c>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -17475,6 +18585,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -17551,6 +18666,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -17627,6 +18747,11 @@
           <t>UGEL LORETO - NAUTA</t>
         </is>
       </c>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -17701,6 +18826,11 @@
           <t>UGEL LORETO - NAUTA</t>
         </is>
       </c>
+      <c r="S226" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -17777,6 +18907,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -17853,6 +18988,11 @@
           <t>UGEL REQUENA</t>
         </is>
       </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -17927,6 +19067,11 @@
           <t>UGEL REQUENA</t>
         </is>
       </c>
+      <c r="S229" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -18003,6 +19148,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -18079,6 +19229,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -18155,6 +19310,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -18235,6 +19395,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="S233" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -18315,6 +19480,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -18395,6 +19565,11 @@
           <t>UGEL MORROPÓN</t>
         </is>
       </c>
+      <c r="S235" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -18471,6 +19646,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="S236" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -18547,6 +19727,11 @@
           <t>UGEL MAYNAS</t>
         </is>
       </c>
+      <c r="S237" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -18621,6 +19806,11 @@
           <t>UGEL MAYNAS</t>
         </is>
       </c>
+      <c r="S238" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -18697,6 +19887,11 @@
           <t>UGEL ALTO AMAZONAS-SAN LORENZO</t>
         </is>
       </c>
+      <c r="S239" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -18771,6 +19966,11 @@
           <t>UGEL ALTO AMAZONAS-SAN LORENZO</t>
         </is>
       </c>
+      <c r="S240" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -18847,6 +20047,11 @@
           <t>UGEL FERREÑAFE</t>
         </is>
       </c>
+      <c r="S241" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -18923,6 +20128,11 @@
           <t>UGEL ALTO AMAZONAS-SAN LORENZO</t>
         </is>
       </c>
+      <c r="S242" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -18997,6 +20207,11 @@
           <t>UGEL ALTO AMAZONAS-SAN LORENZO</t>
         </is>
       </c>
+      <c r="S243" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -19073,6 +20288,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="S244" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -19149,6 +20369,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="S245" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -19225,6 +20450,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="S246" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -19301,6 +20531,11 @@
           <t>UGEL ALTO AMAZONAS-SAN LORENZO</t>
         </is>
       </c>
+      <c r="S247" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -19375,6 +20610,11 @@
           <t>UGEL ALTO AMAZONAS-SAN LORENZO</t>
         </is>
       </c>
+      <c r="S248" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -19451,6 +20691,11 @@
           <t>UGEL ALTO AMAZONAS-YURIMAGUAS</t>
         </is>
       </c>
+      <c r="S249" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -19525,6 +20770,11 @@
           <t>UGEL ALTO AMAZONAS-YURIMAGUAS</t>
         </is>
       </c>
+      <c r="S250" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -19601,6 +20851,11 @@
           <t>UGEL ALTO AMAZONAS-YURIMAGUAS</t>
         </is>
       </c>
+      <c r="S251" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -19677,6 +20932,11 @@
           <t>UGEL ALTO AMAZONAS-YURIMAGUAS</t>
         </is>
       </c>
+      <c r="S252" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -19751,6 +21011,11 @@
           <t>UGEL ALTO AMAZONAS-YURIMAGUAS</t>
         </is>
       </c>
+      <c r="S253" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -19827,6 +21092,11 @@
           <t>UGEL ALTO AMAZONAS-YURIMAGUAS</t>
         </is>
       </c>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -19901,6 +21171,11 @@
           <t>UGEL ALTO AMAZONAS-YURIMAGUAS</t>
         </is>
       </c>
+      <c r="S255" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -19977,6 +21252,11 @@
           <t>UGEL ALTO AMAZONAS-SAN LORENZO</t>
         </is>
       </c>
+      <c r="S256" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -20051,6 +21331,11 @@
           <t>UGEL ALTO AMAZONAS-SAN LORENZO</t>
         </is>
       </c>
+      <c r="S257" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -20127,6 +21412,11 @@
           <t>UGEL LA UNIÓN</t>
         </is>
       </c>
+      <c r="S258" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -20203,6 +21493,11 @@
           <t>UGEL LA UNIÓN</t>
         </is>
       </c>
+      <c r="S259" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -20279,6 +21574,11 @@
           <t>UGEL LA UNIÓN</t>
         </is>
       </c>
+      <c r="S260" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -20355,6 +21655,11 @@
           <t>UGEL LA UNIÓN</t>
         </is>
       </c>
+      <c r="S261" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -20431,6 +21736,11 @@
           <t>UGEL TAMBOGRANDE</t>
         </is>
       </c>
+      <c r="S262" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -20507,6 +21817,11 @@
           <t>UGEL TAMBOGRANDE</t>
         </is>
       </c>
+      <c r="S263" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -20583,6 +21898,11 @@
           <t>UGEL TAMBOGRANDE</t>
         </is>
       </c>
+      <c r="S264" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -20659,6 +21979,11 @@
           <t>UGEL TAMBOGRANDE</t>
         </is>
       </c>
+      <c r="S265" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -20735,6 +22060,11 @@
           <t>UGEL TAMBOGRANDE</t>
         </is>
       </c>
+      <c r="S266" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -20811,6 +22141,11 @@
           <t>UGEL TAMBOGRANDE</t>
         </is>
       </c>
+      <c r="S267" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -20887,6 +22222,11 @@
           <t>UGEL MORROPÓN</t>
         </is>
       </c>
+      <c r="S268" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -20963,6 +22303,11 @@
           <t>UGEL SULLANA</t>
         </is>
       </c>
+      <c r="S269" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -21039,6 +22384,11 @@
           <t>UGEL LAMAS</t>
         </is>
       </c>
+      <c r="S270" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -21113,6 +22463,11 @@
           <t>UGEL LAMAS</t>
         </is>
       </c>
+      <c r="S271" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -21189,6 +22544,11 @@
           <t>UGEL PICOTA</t>
         </is>
       </c>
+      <c r="S272" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -21265,6 +22625,11 @@
           <t>UGEL TOCACHE</t>
         </is>
       </c>
+      <c r="S273" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -21339,6 +22704,11 @@
           <t>UGEL TOCACHE</t>
         </is>
       </c>
+      <c r="S274" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -21415,6 +22785,11 @@
           <t>UGEL TOCACHE</t>
         </is>
       </c>
+      <c r="S275" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -21489,6 +22864,11 @@
           <t>UGEL TOCACHE</t>
         </is>
       </c>
+      <c r="S276" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -21565,6 +22945,11 @@
           <t>UGEL TOCACHE</t>
         </is>
       </c>
+      <c r="S277" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -21641,6 +23026,11 @@
           <t>UGEL ALTO AMAZONAS-SAN LORENZO</t>
         </is>
       </c>
+      <c r="S278" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -21715,6 +23105,11 @@
           <t>UGEL ALTO AMAZONAS-SAN LORENZO</t>
         </is>
       </c>
+      <c r="S279" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -21791,6 +23186,11 @@
           <t>UGEL ALTO AMAZONAS-YURIMAGUAS</t>
         </is>
       </c>
+      <c r="S280" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -21865,6 +23265,11 @@
           <t>UGEL ALTO AMAZONAS-YURIMAGUAS</t>
         </is>
       </c>
+      <c r="S281" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -21941,6 +23346,11 @@
           <t>UGEL LA UNIÓN</t>
         </is>
       </c>
+      <c r="S282" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -22017,6 +23427,11 @@
           <t>UGEL TAMBOGRANDE</t>
         </is>
       </c>
+      <c r="S283" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -22091,6 +23506,11 @@
           <t>UGEL PICOTA</t>
         </is>
       </c>
+      <c r="S284" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -22167,6 +23587,11 @@
           <t>UGEL PICOTA</t>
         </is>
       </c>
+      <c r="S285" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -22241,6 +23666,11 @@
           <t>UGEL PICOTA</t>
         </is>
       </c>
+      <c r="S286" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -22317,6 +23747,11 @@
           <t>UGEL PICOTA</t>
         </is>
       </c>
+      <c r="S287" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -22391,6 +23826,11 @@
           <t>UGEL PICOTA</t>
         </is>
       </c>
+      <c r="S288" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -22467,6 +23907,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="S289" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -22543,6 +23988,11 @@
           <t>UGEL SULLANA</t>
         </is>
       </c>
+      <c r="S290" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -22619,6 +24069,11 @@
           <t>UGEL SULLANA</t>
         </is>
       </c>
+      <c r="S291" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -22699,6 +24154,11 @@
           <t>UGEL CHICLAYO</t>
         </is>
       </c>
+      <c r="S292" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -22779,6 +24239,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="S293" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -22855,6 +24320,11 @@
           <t>UGEL CHICLAYO</t>
         </is>
       </c>
+      <c r="S294" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -22931,6 +24401,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="S295" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -23007,6 +24482,11 @@
           <t>UGEL HUARMACA</t>
         </is>
       </c>
+      <c r="S296" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -23083,6 +24563,11 @@
           <t>UGEL HUARMACA</t>
         </is>
       </c>
+      <c r="S297" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -23159,6 +24644,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="S298" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -23235,6 +24725,11 @@
           <t>UGEL SULLANA</t>
         </is>
       </c>
+      <c r="S299" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -23311,6 +24806,11 @@
           <t>UGEL SULLANA</t>
         </is>
       </c>
+      <c r="S300" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -23387,6 +24887,11 @@
           <t>UGEL SULLANA</t>
         </is>
       </c>
+      <c r="S301" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -23463,6 +24968,11 @@
           <t>UGEL TUMBES</t>
         </is>
       </c>
+      <c r="S302" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -23539,6 +25049,11 @@
           <t>UGEL TUMBES</t>
         </is>
       </c>
+      <c r="S303" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -23615,6 +25130,11 @@
           <t>UGEL TUMBES</t>
         </is>
       </c>
+      <c r="S304" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -23691,6 +25211,11 @@
           <t>UGEL TUMBES</t>
         </is>
       </c>
+      <c r="S305" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -23767,6 +25292,11 @@
           <t>UGEL TUMBES</t>
         </is>
       </c>
+      <c r="S306" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -23843,6 +25373,11 @@
           <t>UGEL TUMBES</t>
         </is>
       </c>
+      <c r="S307" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -23919,6 +25454,11 @@
           <t>UGEL TUMBES</t>
         </is>
       </c>
+      <c r="S308" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -23995,6 +25535,11 @@
           <t>UGEL ZARUMILLA</t>
         </is>
       </c>
+      <c r="S309" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -24071,6 +25616,11 @@
           <t>UGEL ZARUMILLA</t>
         </is>
       </c>
+      <c r="S310" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -24147,6 +25697,11 @@
           <t>UGEL ALTO AMAZONAS-YURIMAGUAS</t>
         </is>
       </c>
+      <c r="S311" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -24221,6 +25776,11 @@
           <t>UGEL ALTO AMAZONAS-YURIMAGUAS</t>
         </is>
       </c>
+      <c r="S312" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -24297,6 +25857,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="S313" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -24373,6 +25938,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="S314" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -24449,6 +26019,11 @@
           <t>UGEL ALTO AMAZONAS-SAN LORENZO</t>
         </is>
       </c>
+      <c r="S315" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -24523,6 +26098,11 @@
           <t>UGEL ALTO AMAZONAS-SAN LORENZO</t>
         </is>
       </c>
+      <c r="S316" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -24599,6 +26179,11 @@
           <t>UGEL TUMBES</t>
         </is>
       </c>
+      <c r="S317" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -24675,6 +26260,11 @@
           <t>UGEL FERREÑAFE</t>
         </is>
       </c>
+      <c r="S318" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -24751,6 +26341,11 @@
           <t>UGEL ZARUMILLA</t>
         </is>
       </c>
+      <c r="S319" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -24827,6 +26422,11 @@
           <t>UGEL ALTO AMAZONAS-SAN LORENZO</t>
         </is>
       </c>
+      <c r="S320" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -24901,6 +26501,11 @@
           <t>UGEL ALTO AMAZONAS-SAN LORENZO</t>
         </is>
       </c>
+      <c r="S321" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -24977,6 +26582,11 @@
           <t>UGEL HUANCABAMBA</t>
         </is>
       </c>
+      <c r="S322" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -25053,6 +26663,11 @@
           <t>UGEL SULLANA</t>
         </is>
       </c>
+      <c r="S323" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -25129,6 +26744,11 @@
           <t>UGEL ZARUMILLA</t>
         </is>
       </c>
+      <c r="S324" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -25205,6 +26825,11 @@
           <t>UGEL TUMBES</t>
         </is>
       </c>
+      <c r="S325" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -25281,6 +26906,11 @@
           <t>UGEL TUMBES</t>
         </is>
       </c>
+      <c r="S326" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -25357,6 +26987,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="S327" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -25437,6 +27072,11 @@
           <t>UGEL MORROPÓN</t>
         </is>
       </c>
+      <c r="S328" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -25513,6 +27153,11 @@
           <t>UGEL CHICLAYO</t>
         </is>
       </c>
+      <c r="S329" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -25593,6 +27238,11 @@
           <t>UGEL FERREÑAFE</t>
         </is>
       </c>
+      <c r="S330" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -25673,6 +27323,11 @@
           <t>UGEL FERREÑAFE</t>
         </is>
       </c>
+      <c r="S331" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -25753,6 +27408,11 @@
           <t>UGEL CHICLAYO</t>
         </is>
       </c>
+      <c r="S332" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -25833,6 +27493,11 @@
           <t>UGEL FERREÑAFE</t>
         </is>
       </c>
+      <c r="S333" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -25907,6 +27572,11 @@
           <t>UGEL CONDORCANQUI</t>
         </is>
       </c>
+      <c r="S334" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -25981,6 +27651,11 @@
           <t>UGEL CONDORCANQUI</t>
         </is>
       </c>
+      <c r="S335" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -26061,6 +27736,11 @@
           <t>UGEL TUMBES</t>
         </is>
       </c>
+      <c r="S336" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -26141,6 +27821,11 @@
           <t>UGEL CONTRALMIRANTE VILLAR</t>
         </is>
       </c>
+      <c r="S337" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -26215,6 +27900,11 @@
           <t>UGEL CONDORCANQUI</t>
         </is>
       </c>
+      <c r="S338" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -26289,6 +27979,11 @@
           <t>UGEL CONDORCANQUI</t>
         </is>
       </c>
+      <c r="S339" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -26363,6 +28058,11 @@
           <t>UGEL CONDORCANQUI</t>
         </is>
       </c>
+      <c r="S340" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -26437,6 +28137,11 @@
           <t>UGEL CONDORCANQUI</t>
         </is>
       </c>
+      <c r="S341" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -26511,6 +28216,11 @@
           <t>UGEL 08 CAÑETE</t>
         </is>
       </c>
+      <c r="S342" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -26591,6 +28301,11 @@
           <t>UGEL VÍCTOR FAJARDO</t>
         </is>
       </c>
+      <c r="S343" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -26671,6 +28386,11 @@
           <t>UGEL VÍCTOR FAJARDO</t>
         </is>
       </c>
+      <c r="S344" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -26751,6 +28471,11 @@
           <t>UGEL VÍCTOR FAJARDO</t>
         </is>
       </c>
+      <c r="S345" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -26827,6 +28552,11 @@
           <t>UGEL TAMBOGRANDE</t>
         </is>
       </c>
+      <c r="S346" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -26903,6 +28633,11 @@
           <t>UGEL HUARMACA</t>
         </is>
       </c>
+      <c r="S347" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -26979,6 +28714,11 @@
           <t>UGEL CHULUCANAS</t>
         </is>
       </c>
+      <c r="S348" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -27055,6 +28795,11 @@
           <t>UGEL AYABACA</t>
         </is>
       </c>
+      <c r="S349" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -27131,6 +28876,11 @@
           <t>UGEL SECHURA</t>
         </is>
       </c>
+      <c r="S350" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -27207,6 +28957,11 @@
           <t>UGEL SECHURA</t>
         </is>
       </c>
+      <c r="S351" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -27283,6 +29038,11 @@
           <t>UGEL TAMBOGRANDE</t>
         </is>
       </c>
+      <c r="S352" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -27359,6 +29119,11 @@
           <t>UGEL CHULUCANAS</t>
         </is>
       </c>
+      <c r="S353" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -27435,6 +29200,11 @@
           <t>UGEL MORROPÓN</t>
         </is>
       </c>
+      <c r="S354" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -27511,6 +29281,11 @@
           <t>UGEL SECHURA</t>
         </is>
       </c>
+      <c r="S355" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -27587,6 +29362,11 @@
           <t>UGEL CHULUCANAS</t>
         </is>
       </c>
+      <c r="S356" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -27667,6 +29447,11 @@
           <t>UGEL CHICLAYO</t>
         </is>
       </c>
+      <c r="S357" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -27747,6 +29532,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="S358" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -27823,6 +29613,11 @@
           <t>UGEL LUYA</t>
         </is>
       </c>
+      <c r="S359" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -27899,6 +29694,11 @@
           <t>UGEL YUNGAY</t>
         </is>
       </c>
+      <c r="S360" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -27975,6 +29775,11 @@
           <t>UGEL PARINACOCHAS</t>
         </is>
       </c>
+      <c r="S361" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -28051,6 +29856,11 @@
           <t>UGEL CAJAMARCA</t>
         </is>
       </c>
+      <c r="S362" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -28127,6 +29937,11 @@
           <t>UGEL JAN</t>
         </is>
       </c>
+      <c r="S363" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -28203,6 +30018,11 @@
           <t>UGEL JAN</t>
         </is>
       </c>
+      <c r="S364" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -28279,6 +30099,11 @@
           <t>UGEL JAN</t>
         </is>
       </c>
+      <c r="S365" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -28355,6 +30180,11 @@
           <t>UGEL JAN</t>
         </is>
       </c>
+      <c r="S366" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -28431,6 +30261,11 @@
           <t>UGEL SANTA CRUZ</t>
         </is>
       </c>
+      <c r="S367" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -28507,6 +30342,11 @@
           <t>UGEL HUÁNUCO</t>
         </is>
       </c>
+      <c r="S368" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -28583,6 +30423,11 @@
           <t>UGEL ICA</t>
         </is>
       </c>
+      <c r="S369" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -28659,6 +30504,11 @@
           <t>UGEL ICA</t>
         </is>
       </c>
+      <c r="S370" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -28735,6 +30585,11 @@
           <t>UGEL ICA</t>
         </is>
       </c>
+      <c r="S371" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -28811,6 +30666,11 @@
           <t>UGEL PALPA</t>
         </is>
       </c>
+      <c r="S372" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -28887,6 +30747,11 @@
           <t>UGEL PALPA</t>
         </is>
       </c>
+      <c r="S373" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -28963,6 +30828,11 @@
           <t>UGEL NASCA</t>
         </is>
       </c>
+      <c r="S374" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -29039,6 +30909,11 @@
           <t>UGEL PISCO</t>
         </is>
       </c>
+      <c r="S375" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -29115,6 +30990,11 @@
           <t>UGEL CHANCHAMAYO</t>
         </is>
       </c>
+      <c r="S376" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -29189,6 +31069,11 @@
       <c r="R377" t="inlineStr">
         <is>
           <t>UGEL CHANCHAMAYO</t>
+        </is>
+      </c>
+      <c r="S377" t="inlineStr">
+        <is>
+          <t>UGME</t>
         </is>
       </c>
     </row>
@@ -29239,6 +31124,11 @@
       <c r="P378" t="inlineStr"/>
       <c r="Q378" t="inlineStr"/>
       <c r="R378" t="inlineStr"/>
+      <c r="S378" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -29315,6 +31205,11 @@
           <t>UGEL SATIPO</t>
         </is>
       </c>
+      <c r="S379" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -29391,6 +31286,11 @@
           <t>UGEL TARMA</t>
         </is>
       </c>
+      <c r="S380" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -29467,6 +31367,11 @@
           <t>UGEL SÁNCHEZ CARRIÓN</t>
         </is>
       </c>
+      <c r="S381" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -29543,6 +31448,11 @@
           <t>UGEL SÁNCHEZ CARRIÓN</t>
         </is>
       </c>
+      <c r="S382" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -29619,6 +31529,11 @@
           <t>UGEL GRAN CHIMÚ</t>
         </is>
       </c>
+      <c r="S383" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -29695,6 +31610,11 @@
           <t>UGEL CHICLAYO</t>
         </is>
       </c>
+      <c r="S384" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -29771,6 +31691,11 @@
           <t>UGEL CHICLAYO</t>
         </is>
       </c>
+      <c r="S385" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -29847,6 +31772,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="S386" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -29923,6 +31853,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="S387" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -29999,6 +31934,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="S388" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -30075,6 +32015,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="S389" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -30151,6 +32096,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="S390" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -30227,6 +32177,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="S391" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -30303,6 +32258,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="S392" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -30379,6 +32339,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="S393" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -30455,6 +32420,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="S394" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -30531,6 +32501,11 @@
           <t>UGEL 08 CAÑETE</t>
         </is>
       </c>
+      <c r="S395" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -30607,6 +32582,11 @@
           <t>UGEL 15 HUAROCHIRÍ</t>
         </is>
       </c>
+      <c r="S396" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -30683,6 +32663,11 @@
           <t>UGEL ALTO AMAZONAS-YURIMAGUAS</t>
         </is>
       </c>
+      <c r="S397" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -30759,6 +32744,11 @@
           <t>UGEL CARABAYA</t>
         </is>
       </c>
+      <c r="S398" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -30835,6 +32825,11 @@
           <t>UGEL CARABAYA</t>
         </is>
       </c>
+      <c r="S399" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -30911,6 +32906,11 @@
           <t>UGEL SANDIA</t>
         </is>
       </c>
+      <c r="S400" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -30987,6 +32987,11 @@
           <t>UGEL SANDIA</t>
         </is>
       </c>
+      <c r="S401" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -31063,6 +33068,11 @@
           <t>UGEL TUMBES</t>
         </is>
       </c>
+      <c r="S402" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -31139,6 +33149,11 @@
           <t>UGEL TUMBES</t>
         </is>
       </c>
+      <c r="S403" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -31215,6 +33230,11 @@
           <t>UGEL TUMBES</t>
         </is>
       </c>
+      <c r="S404" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -31291,6 +33311,11 @@
           <t>UGEL TUMBES</t>
         </is>
       </c>
+      <c r="S405" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -31367,6 +33392,11 @@
           <t>UGEL ZARUMILLA</t>
         </is>
       </c>
+      <c r="S406" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
@@ -31443,6 +33473,11 @@
           <t>UGEL ZARUMILLA</t>
         </is>
       </c>
+      <c r="S407" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -31519,6 +33554,11 @@
           <t>UGEL CORONEL PORTILLO</t>
         </is>
       </c>
+      <c r="S408" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
@@ -31595,6 +33635,11 @@
           <t>UGEL CORONEL PORTILLO</t>
         </is>
       </c>
+      <c r="S409" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -31671,6 +33716,11 @@
           <t>UGEL PADRE ABAD</t>
         </is>
       </c>
+      <c r="S410" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -31747,6 +33797,11 @@
           <t>UGEL HUANTA</t>
         </is>
       </c>
+      <c r="S411" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -31823,6 +33878,11 @@
           <t>UGEL SAN MIGUEL</t>
         </is>
       </c>
+      <c r="S412" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -31899,6 +33959,11 @@
           <t>UGEL ICA</t>
         </is>
       </c>
+      <c r="S413" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -31975,6 +34040,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="S414" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -32051,6 +34121,11 @@
           <t>UGEL SANDIA</t>
         </is>
       </c>
+      <c r="S415" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -32127,6 +34202,11 @@
           <t>UGEL SANDIA</t>
         </is>
       </c>
+      <c r="S416" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
@@ -32203,6 +34283,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="S417" t="inlineStr">
+        <is>
+          <t>UGME</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -32277,6 +34362,11 @@
       <c r="R418" t="inlineStr">
         <is>
           <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="S418" t="inlineStr">
+        <is>
+          <t>UGME</t>
         </is>
       </c>
     </row>

--- a/output/bases_limpias/Grupo_03_MODULOS/df_ugme_modulares.xlsx
+++ b/output/bases_limpias/Grupo_03_MODULOS/df_ugme_modulares.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S418"/>
+  <dimension ref="A1:U418"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +509,16 @@
       </c>
       <c r="S1" t="inlineStr">
         <is>
+          <t>nombre_ie</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
           <t>fuente</t>
         </is>
       </c>
@@ -590,6 +600,16 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
+          <t>86012/86012</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -671,6 +691,16 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
+          <t>86648 SANTO DOMINGO DE GUZMAN/86648 SANTO DOMINGO DE GUZMAN</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -752,6 +782,16 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
+          <t>86648 SANTO DOMINGO DE GUZMAN/86648 SANTO DOMINGO DE GUZMAN</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -833,6 +873,16 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
+          <t>38099</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -914,6 +964,16 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
+          <t>24229 SOCRATES ZUZUNAGA HUAITA</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -995,6 +1055,16 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
+          <t>80608</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -1076,6 +1146,16 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
+          <t>80534 CIRO ALEGRIA BAZAN/80534 CIRO ALEGRIA BAZAN/80534 CIRO ALEGRIA BAZAN</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -1157,6 +1237,16 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
+          <t>81550/81550</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -1238,6 +1328,16 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
+          <t>82013 JORGE CHAVEZ/82013 JORGE CHAVEZ/82013 JORGE CHAVEZ</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -1323,6 +1423,16 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
+          <t>11092 MANUEL ANTONIO MESONES MURO</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -1404,6 +1514,16 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
+          <t>62535/62535</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -1483,6 +1603,16 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
+          <t>62535/62535</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -1564,6 +1694,16 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
+          <t>601054/601054</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -1643,6 +1783,16 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
+          <t>601054/601054</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -1724,6 +1874,16 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
+          <t>60741 JOSE SILVERIO BALANDRA/60741 JOSE SILVERIO BALANDRA</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -1803,6 +1963,16 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
+          <t>60741 JOSE SILVERIO BALANDRA/60741 JOSE SILVERIO BALANDRA</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -1884,6 +2054,16 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
+          <t>64232</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -1963,6 +2143,16 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
+          <t>64232</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -2044,6 +2234,16 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
+          <t>20124</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -2125,6 +2325,16 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
+          <t>14061/14061/14061</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -2206,6 +2416,16 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -2287,6 +2507,16 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
+          <t>14195/14195</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -2368,6 +2598,16 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
+          <t>14195/14195</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -2449,6 +2689,16 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
+          <t>TEOFILO FLORES HUAMAN/TEOFILO FLORES HUAMAN/TEOFILO FLORES HUAMAN</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -2530,6 +2780,16 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
+          <t>TEOFILO FLORES HUAMAN/TEOFILO FLORES HUAMAN/TEOFILO FLORES HUAMAN</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -2611,6 +2871,16 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -2692,6 +2962,16 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
+          <t>14274/14274</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -2773,6 +3053,16 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
+          <t>14443/14443</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -2854,6 +3144,16 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
+          <t>14466 CESAR TRELLES LARA/14466 CESAR TRELLES LARA/14466 CESAR TRELLES LARA</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -2935,6 +3235,16 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
+          <t>20194</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -3016,6 +3326,16 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
+          <t>SEÑOR DE LA EXALTACION COLLONAYUC/SEÑOR DE LA EXALTACION COLLONAYUC/SEÑOR DE LA EXALTACION COLLONAYUC</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -3097,6 +3417,16 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
+          <t>CRISTO REY/CRISTO REY</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -3178,6 +3508,16 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
+          <t>CRISTO REY/CRISTO REY</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -3259,6 +3599,16 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
+          <t>IGNACIO MERINO MUÑOZ/IGNACIO MERINO MUÑOZ</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -3340,6 +3690,16 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
+          <t>IGNACIO MERINO MUÑOZ/IGNACIO MERINO MUÑOZ</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -3421,6 +3781,16 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
+          <t>15047 ANTONIO RAIMONDI/15047 ANTONIO RAIMONDI/15047 ANTONIO RAIMONDI</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -3502,6 +3872,16 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
+          <t>15212 JUAN VELASCO ALVARADO/15212 JUAN VELASCO ALVARADO</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -3583,6 +3963,16 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
+          <t>20035/20035</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -3664,6 +4054,16 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
+          <t>20035/20035</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -3745,6 +4145,16 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
+          <t>090</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -3826,6 +4236,16 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
+          <t>433</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -3907,6 +4327,16 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
+          <t>14630</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -3988,6 +4418,16 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
+          <t>15022 JUAN PALACIOS PINTADO/15022 JUAN PALACIOS PINTADO/15022 JUAN PALACIOS PINTADO/15022 JUAN PALACIOS PINTADO</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -4069,6 +4509,16 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
+          <t>15022 JUAN PALACIOS PINTADO/15022 JUAN PALACIOS PINTADO/15022 JUAN PALACIOS PINTADO/15022 JUAN PALACIOS PINTADO</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -4150,6 +4600,16 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
+          <t>DOS DE MAYO</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -4231,6 +4691,16 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
+          <t>20105</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -4312,6 +4782,16 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
+          <t>20167</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -4393,6 +4873,16 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
+          <t>15078 SAN PEDRO SAN PABLO/15078 SAN PEDRO SAN PABLO/15078 SAN PEDRO SAN PABLO</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -4474,6 +4964,16 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
+          <t>10411/10411</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -4555,6 +5055,16 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
+          <t>IGNACIO ESCUDERO/IGNACIO ESCUDERO/IGNACIO ESCUDERO</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -4636,6 +5146,16 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
+          <t>14918 TUPAC AMARU/14918 TUPAC AMARU</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -4717,6 +5237,16 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
+          <t>FEDERICO VILLARREAL/FEDERICO VILLARREAL/FEDERICO VILLARREAL</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -4798,6 +5328,16 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
+          <t>014 MIGUEL GRAU/014 MIGUEL GRAU</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -4879,6 +5419,16 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
+          <t>014 MIGUEL GRAU/014 MIGUEL GRAU</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -4960,6 +5510,16 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
+          <t>117 RIGOBERTO MEZA CHUNGA</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -5041,6 +5601,16 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
+          <t>NUEVO HORIZONTE/NUEVO HORIZONTE/REPUBLICA DEL PERU</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -5122,6 +5692,16 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
+          <t>218 LOS JARDINES</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -5203,6 +5783,16 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
+          <t>028 DAGMA ADALIA POZO GARCIA</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -5284,6 +5874,16 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
+          <t>ANDRES ARAUJO/ANDRES ARAUJO</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -5365,6 +5965,16 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
+          <t>035 HORACIO ZEVALLOS GAMEZ/035 HORACIO ZEVALLOS GAMEZ</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -5446,6 +6056,16 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
+          <t>20832/20832</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -5527,6 +6147,16 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
+          <t>20832/20832</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -5608,6 +6238,16 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
+          <t>904</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -5689,6 +6329,16 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
+          <t>62714</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -5768,6 +6418,16 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
+          <t>62714</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -5849,6 +6509,16 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
+          <t>62715</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -5928,6 +6598,16 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
+          <t>62715</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -6009,6 +6689,16 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
+          <t>82152 JOSE ANDRES RAZURI ESTEVES/82152 JOSE ANDRES RAZURI ESTEVES</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -6090,6 +6780,16 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
+          <t>DIVINO NIÑO/DIVINO NIÑO</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -6171,6 +6871,16 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
+          <t>6010221 FRAY JESUS CARBALLO FERNANDEZ/6010221 FRAY JESUS CARBALLO FERNANDEZ</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -6250,6 +6960,16 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
+          <t>6010221 FRAY JESUS CARBALLO FERNANDEZ/6010221 FRAY JESUS CARBALLO FERNANDEZ</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -6331,6 +7051,16 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
+          <t>64740/64740</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -6410,6 +7140,16 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
+          <t>64740/64740</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -6491,6 +7231,16 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
+          <t>64740/64740</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -6572,6 +7322,16 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
+          <t>1292</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -6653,6 +7413,16 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
+          <t>15035 FELIX JOAQUIN SEMINARIO ECHEANDIA</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -6734,6 +7504,16 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
+          <t>SAN JACINTO</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -6815,6 +7595,16 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
+          <t>1543/1543</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -6896,6 +7686,16 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
+          <t>1545</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -6977,6 +7777,16 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
+          <t>20878/20878/20878</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -7058,6 +7868,16 @@
       </c>
       <c r="S82" t="inlineStr">
         <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -7139,6 +7959,16 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
+          <t>14007/14007</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -7220,6 +8050,16 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
+          <t>NUESTRA SEÑORA DE LAS MERCEDES/NUESTRA SEÑORA DE LAS MERCEDES/NUESTRA SEÑORA DE LAS MERCEDES</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -7305,6 +8145,16 @@
       </c>
       <c r="S85" t="inlineStr">
         <is>
+          <t>10172 MARIA ISABEL NUÑEZ FLORES DE SILVA/10172 MARIA ISABEL NUÑEZ FLORES DE SILVA</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -7386,6 +8236,16 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
+          <t>15244/15244</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -7467,6 +8327,16 @@
       </c>
       <c r="S87" t="inlineStr">
         <is>
+          <t>14429 RICARDO HUMBERTO RAMOS PLATA/14429 RICARDO HUMBERTO RAMOS PLATA/14429 RICARDO HUMBERTO RAMOS PLATA</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -7548,6 +8418,16 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
+          <t>15453 SAN FRANCISCO DE ASIS</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -7629,6 +8509,16 @@
       </c>
       <c r="S89" t="inlineStr">
         <is>
+          <t>1501</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -7710,6 +8600,16 @@
       </c>
       <c r="S90" t="inlineStr">
         <is>
+          <t>15071/15071</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -7791,6 +8691,16 @@
       </c>
       <c r="S91" t="inlineStr">
         <is>
+          <t>20849 TUPAC AMARU</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -7872,6 +8782,16 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
+          <t>069</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -7953,6 +8873,16 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
+          <t>015 CORAZON DE MARIA</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -8034,6 +8964,16 @@
       </c>
       <c r="S94" t="inlineStr">
         <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -8115,6 +9055,16 @@
       </c>
       <c r="S95" t="inlineStr">
         <is>
+          <t>055 FIDEL OYOLA ROMERO/055 FIDEL OYOLA ROMERO</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -8196,6 +9146,16 @@
       </c>
       <c r="S96" t="inlineStr">
         <is>
+          <t>PERU JAPON</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -8277,6 +9237,16 @@
       </c>
       <c r="S97" t="inlineStr">
         <is>
+          <t>14129</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -8362,6 +9332,16 @@
       </c>
       <c r="S98" t="inlineStr">
         <is>
+          <t>10098 PEDRO VERA CASIANO</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -8447,6 +9427,16 @@
       </c>
       <c r="S99" t="inlineStr">
         <is>
+          <t>10103/10103</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -8532,6 +9522,16 @@
       </c>
       <c r="S100" t="inlineStr">
         <is>
+          <t>10094 ROSA MURO GUEVARA DE BARRAGAN</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -8617,6 +9617,16 @@
       </c>
       <c r="S101" t="inlineStr">
         <is>
+          <t>11635 INCA PACHACUTEC</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -8702,6 +9712,16 @@
       </c>
       <c r="S102" t="inlineStr">
         <is>
+          <t>15245/15245</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -8787,6 +9807,16 @@
       </c>
       <c r="S103" t="inlineStr">
         <is>
+          <t>SAN JUAN DE LA FRONTERA/SAN JUAN DE LA FRONTERA/SAN JUAN DE LA FRONTERA</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -8870,6 +9900,16 @@
       </c>
       <c r="S104" t="inlineStr">
         <is>
+          <t>11222 SAGRADO CORAZON DE JESUS/11222 SAGRADO CORAZON DE JESUS</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -8951,6 +9991,16 @@
       </c>
       <c r="S105" t="inlineStr">
         <is>
+          <t>14103/14103/14103</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -9032,6 +10082,16 @@
       </c>
       <c r="S106" t="inlineStr">
         <is>
+          <t>CESAR VALLEJO</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -9113,6 +10173,16 @@
       </c>
       <c r="S107" t="inlineStr">
         <is>
+          <t>NUESTRA SEÑORA DE LAS MERCEDES/NUESTRA SEÑORA DE LAS MERCEDES/NUESTRA SEÑORA DE LAS MERCEDES</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -9194,6 +10264,16 @@
       </c>
       <c r="S108" t="inlineStr">
         <is>
+          <t>86133/86133/86133</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -9275,6 +10355,16 @@
       </c>
       <c r="S109" t="inlineStr">
         <is>
+          <t>86133/86133/86133</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -9356,6 +10446,16 @@
       </c>
       <c r="S110" t="inlineStr">
         <is>
+          <t>38054</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -9437,6 +10537,16 @@
       </c>
       <c r="S111" t="inlineStr">
         <is>
+          <t>38578</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -9518,6 +10628,16 @@
       </c>
       <c r="S112" t="inlineStr">
         <is>
+          <t>15225</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -9599,6 +10719,16 @@
       </c>
       <c r="S113" t="inlineStr">
         <is>
+          <t>20165</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -9680,6 +10810,16 @@
       </c>
       <c r="S114" t="inlineStr">
         <is>
+          <t>20179</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -9761,6 +10901,16 @@
       </c>
       <c r="S115" t="inlineStr">
         <is>
+          <t>14658</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -9842,6 +10992,16 @@
       </c>
       <c r="S116" t="inlineStr">
         <is>
+          <t>926 NUEVO AMANECER</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -9923,6 +11083,16 @@
       </c>
       <c r="S117" t="inlineStr">
         <is>
+          <t>432-110</t>
+        </is>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -10004,6 +11174,16 @@
       </c>
       <c r="S118" t="inlineStr">
         <is>
+          <t>86029 ROSA MARIA RAMIREZ ARIAS/86029 ROSA MARIA RAMIREZ ARIAS</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -10085,6 +11265,16 @@
       </c>
       <c r="S119" t="inlineStr">
         <is>
+          <t>86029 ROSA MARIA RAMIREZ ARIAS/86029 ROSA MARIA RAMIREZ ARIAS</t>
+        </is>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -10170,6 +11360,16 @@
       </c>
       <c r="S120" t="inlineStr">
         <is>
+          <t>15138/15138/15138</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -10251,6 +11451,16 @@
       </c>
       <c r="S121" t="inlineStr">
         <is>
+          <t>475</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -10332,6 +11542,16 @@
       </c>
       <c r="S122" t="inlineStr">
         <is>
+          <t>ALONSO DE ALVARADO</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -10411,6 +11631,16 @@
       </c>
       <c r="S123" t="inlineStr">
         <is>
+          <t>ALONSO DE ALVARADO</t>
+        </is>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -10496,6 +11726,16 @@
       </c>
       <c r="S124" t="inlineStr">
         <is>
+          <t>LUIS VALLEJOS SANTONI</t>
+        </is>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -10581,6 +11821,16 @@
       </c>
       <c r="S125" t="inlineStr">
         <is>
+          <t>3074 PEDRO RUIZ GALLO/3074 PEDRO RUIZ GALLO/3074 PEDRO RUIZ GALLO</t>
+        </is>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -10666,6 +11916,16 @@
       </c>
       <c r="S126" t="inlineStr">
         <is>
+          <t>2095 HERMAN BUSSE DE LA GUERRA/2095 HERMAN BUSSE DE LA GUERRA/2095 HERMAN BUSSE DE LA GUERRA/2095 HERMAN BUSSE DE LA GUERRA</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -10751,6 +12011,16 @@
       </c>
       <c r="S127" t="inlineStr">
         <is>
+          <t>7260 SEÑOR DE LOS MILAGROS/7260 SEÑOR DE LOS MILAGROS</t>
+        </is>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -10836,6 +12106,16 @@
       </c>
       <c r="S128" t="inlineStr">
         <is>
+          <t>1178 JAVIER HERAUD/1178 JAVIER HERAUD</t>
+        </is>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -10921,6 +12201,16 @@
       </c>
       <c r="S129" t="inlineStr">
         <is>
+          <t>ANTONIA MORENO DE CACERES/ANTONIA MORENO DE CACERES/ANTONIA MORENO DE CACERES</t>
+        </is>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -11006,6 +12296,16 @@
       </c>
       <c r="S130" t="inlineStr">
         <is>
+          <t>157 CAPITAN FAP JOSE ABELARDO QUIÑONEZ</t>
+        </is>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -11091,6 +12391,16 @@
       </c>
       <c r="S131" t="inlineStr">
         <is>
+          <t>20407/20407</t>
+        </is>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -11170,6 +12480,16 @@
       </c>
       <c r="S132" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -11255,6 +12575,16 @@
       </c>
       <c r="S133" t="inlineStr">
         <is>
+          <t>JUAN DE DIOS GUEVARA</t>
+        </is>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -11340,6 +12670,16 @@
       </c>
       <c r="S134" t="inlineStr">
         <is>
+          <t>MI PEQUEÑO MUNDO/MI PEQUEÑO MUNDO</t>
+        </is>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -11421,6 +12761,16 @@
       </c>
       <c r="S135" t="inlineStr">
         <is>
+          <t>16795/16795</t>
+        </is>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -11500,6 +12850,16 @@
       </c>
       <c r="S136" t="inlineStr">
         <is>
+          <t>16795/16795</t>
+        </is>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -11581,6 +12941,16 @@
       </c>
       <c r="S137" t="inlineStr">
         <is>
+          <t>0026/0026</t>
+        </is>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -11660,6 +13030,16 @@
       </c>
       <c r="S138" t="inlineStr">
         <is>
+          <t>0026/0026</t>
+        </is>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -11741,6 +13121,16 @@
       </c>
       <c r="S139" t="inlineStr">
         <is>
+          <t>64478 BILINGUE INTERCULTURAL/64478 BILINGUE INTERCULTURAL</t>
+        </is>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -11822,6 +13212,16 @@
       </c>
       <c r="S140" t="inlineStr">
         <is>
+          <t>64478 BILINGUE INTERCULTURAL/64478 BILINGUE INTERCULTURAL</t>
+        </is>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -11907,6 +13307,16 @@
       </c>
       <c r="S141" t="inlineStr">
         <is>
+          <t>84086 FRANCISCO BOLOGNESI CERVANTES/84086 FRANCISCO BOLOGNESI CERVANTES</t>
+        </is>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -11992,6 +13402,16 @@
       </c>
       <c r="S142" t="inlineStr">
         <is>
+          <t>50508</t>
+        </is>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -12077,6 +13497,16 @@
       </c>
       <c r="S143" t="inlineStr">
         <is>
+          <t>16023 VICTOR TORRES ARENAS/16023</t>
+        </is>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -12162,6 +13592,16 @@
       </c>
       <c r="S144" t="inlineStr">
         <is>
+          <t>50482</t>
+        </is>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -12247,6 +13687,16 @@
       </c>
       <c r="S145" t="inlineStr">
         <is>
+          <t>821639/821639</t>
+        </is>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -12332,6 +13782,16 @@
       </c>
       <c r="S146" t="inlineStr">
         <is>
+          <t>54200</t>
+        </is>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -12417,6 +13877,16 @@
       </c>
       <c r="S147" t="inlineStr">
         <is>
+          <t>84276</t>
+        </is>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -12502,6 +13972,16 @@
       </c>
       <c r="S148" t="inlineStr">
         <is>
+          <t>KUNTUR KALLPA</t>
+        </is>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -12587,6 +14067,16 @@
       </c>
       <c r="S149" t="inlineStr">
         <is>
+          <t>16647 HUMBERTO ALDAZ PEZANTES/16647 HUMBERTO ALDAZ PEZANTES</t>
+        </is>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -12672,6 +14162,16 @@
       </c>
       <c r="S150" t="inlineStr">
         <is>
+          <t>18421</t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -12753,6 +14253,16 @@
       </c>
       <c r="S151" t="inlineStr">
         <is>
+          <t>20396 ANTONIO ARELLANO BUITRON/20396 ANTONIO ARELLANO BUITRON/20396 ANTONIO ARELLANO BUITRON</t>
+        </is>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -12838,6 +14348,16 @@
       </c>
       <c r="S152" t="inlineStr">
         <is>
+          <t>821013/821013</t>
+        </is>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -12923,6 +14443,16 @@
       </c>
       <c r="S153" t="inlineStr">
         <is>
+          <t>SOL Y MAR/SOL Y MAR</t>
+        </is>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -13008,6 +14538,16 @@
       </c>
       <c r="S154" t="inlineStr">
         <is>
+          <t>17808</t>
+        </is>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -13093,6 +14633,16 @@
       </c>
       <c r="S155" t="inlineStr">
         <is>
+          <t>MARIA AUXILIADORA</t>
+        </is>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -13172,6 +14722,16 @@
       </c>
       <c r="S156" t="inlineStr">
         <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -13251,6 +14811,16 @@
       </c>
       <c r="S157" t="inlineStr">
         <is>
+          <t>442</t>
+        </is>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -13330,6 +14900,16 @@
       </c>
       <c r="S158" t="inlineStr">
         <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -13409,6 +14989,16 @@
       </c>
       <c r="S159" t="inlineStr">
         <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -13488,6 +15078,16 @@
       </c>
       <c r="S160" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -13567,6 +15167,16 @@
       </c>
       <c r="S161" t="inlineStr">
         <is>
+          <t>17884</t>
+        </is>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -13646,6 +15256,16 @@
       </c>
       <c r="S162" t="inlineStr">
         <is>
+          <t>17885</t>
+        </is>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -13725,6 +15345,16 @@
       </c>
       <c r="S163" t="inlineStr">
         <is>
+          <t>17091</t>
+        </is>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -13804,6 +15434,16 @@
       </c>
       <c r="S164" t="inlineStr">
         <is>
+          <t>17828</t>
+        </is>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -13883,6 +15523,16 @@
       </c>
       <c r="S165" t="inlineStr">
         <is>
+          <t>18857</t>
+        </is>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -13962,6 +15612,16 @@
       </c>
       <c r="S166" t="inlineStr">
         <is>
+          <t>17886</t>
+        </is>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -14041,6 +15701,16 @@
       </c>
       <c r="S167" t="inlineStr">
         <is>
+          <t>NICOLAS DE PIEROLA</t>
+        </is>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -14120,6 +15790,16 @@
       </c>
       <c r="S168" t="inlineStr">
         <is>
+          <t>ALTO PAJACUSA</t>
+        </is>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -14199,6 +15879,16 @@
       </c>
       <c r="S169" t="inlineStr">
         <is>
+          <t>HECTOR PEAS TSEGKUAN</t>
+        </is>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -14278,6 +15968,16 @@
       </c>
       <c r="S170" t="inlineStr">
         <is>
+          <t>MOISES MANCO NUJIGKUS YUMIS</t>
+        </is>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -14357,6 +16057,16 @@
       </c>
       <c r="S171" t="inlineStr">
         <is>
+          <t>ROMAN SHAJIAN SAKEJAT</t>
+        </is>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -14436,6 +16146,16 @@
       </c>
       <c r="S172" t="inlineStr">
         <is>
+          <t>SANTIAGO MANUIN VALERA</t>
+        </is>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -14521,6 +16241,16 @@
       </c>
       <c r="S173" t="inlineStr">
         <is>
+          <t>5137/5137</t>
+        </is>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -14606,6 +16336,16 @@
       </c>
       <c r="S174" t="inlineStr">
         <is>
+          <t>16221 LEONCIO PRADO/16221 LEONCIO PRADO</t>
+        </is>
+      </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -14687,6 +16427,16 @@
       </c>
       <c r="S175" t="inlineStr">
         <is>
+          <t>501458</t>
+        </is>
+      </c>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -14772,6 +16522,16 @@
       </c>
       <c r="S176" t="inlineStr">
         <is>
+          <t>80446 RAMON CASTILLA/80446 RAMON CASTILLA</t>
+        </is>
+      </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -14857,6 +16617,16 @@
       </c>
       <c r="S177" t="inlineStr">
         <is>
+          <t>80445/80445</t>
+        </is>
+      </c>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -14942,6 +16712,16 @@
       </c>
       <c r="S178" t="inlineStr">
         <is>
+          <t>JUAN VELASCO ALVARADO/JUAN VELASCO ALVARADO/JUAN VELASCO ALVARADO</t>
+        </is>
+      </c>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -15027,6 +16807,16 @@
       </c>
       <c r="S179" t="inlineStr">
         <is>
+          <t>CULQUI/CULQUI/CULQUI</t>
+        </is>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -15112,6 +16902,16 @@
       </c>
       <c r="S180" t="inlineStr">
         <is>
+          <t>15321</t>
+        </is>
+      </c>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -15193,6 +16993,16 @@
       </c>
       <c r="S181" t="inlineStr">
         <is>
+          <t>11222 SAGRADO CORAZON DE JESUS/11222 SAGRADO CORAZON DE JESUS</t>
+        </is>
+      </c>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -15274,6 +17084,16 @@
       </c>
       <c r="S182" t="inlineStr">
         <is>
+          <t>11249/11249</t>
+        </is>
+      </c>
+      <c r="T182" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -15355,6 +17175,16 @@
       </c>
       <c r="S183" t="inlineStr">
         <is>
+          <t>058 NIÑO JESUS</t>
+        </is>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -15436,6 +17266,16 @@
       </c>
       <c r="S184" t="inlineStr">
         <is>
+          <t>11508 NUESTRA VIRGEN DE LA PAZ</t>
+        </is>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -15517,6 +17357,16 @@
       </c>
       <c r="S185" t="inlineStr">
         <is>
+          <t>11502 INCA GARCILAZO DE LA VEGA/11502 INCA GARCILAZO DE LA VEGA</t>
+        </is>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -15598,6 +17448,16 @@
       </c>
       <c r="S186" t="inlineStr">
         <is>
+          <t>11502 INCA GARCILAZO DE LA VEGA/11502 INCA GARCILAZO DE LA VEGA</t>
+        </is>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -15679,6 +17539,16 @@
       </c>
       <c r="S187" t="inlineStr">
         <is>
+          <t>11517 SANTA ANA</t>
+        </is>
+      </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -15760,6 +17630,16 @@
       </c>
       <c r="S188" t="inlineStr">
         <is>
+          <t>11035 SANTO DOMINGO SAVIO/11035 SANTO DOMINGO SAVIO/11035 SANTO DOMINGO SAVIO/KARL WEISS</t>
+        </is>
+      </c>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U188" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -15841,6 +17721,16 @@
       </c>
       <c r="S189" t="inlineStr">
         <is>
+          <t>10116 SEÑOR NAZARENO CAUTIVO/10116 SEÑOR NAZARENO CAUTIVO</t>
+        </is>
+      </c>
+      <c r="T189" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U189" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -15922,6 +17812,16 @@
       </c>
       <c r="S190" t="inlineStr">
         <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -16003,6 +17903,16 @@
       </c>
       <c r="S191" t="inlineStr">
         <is>
+          <t>10130</t>
+        </is>
+      </c>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -16084,6 +17994,16 @@
       </c>
       <c r="S192" t="inlineStr">
         <is>
+          <t>10141 - 7 DE NOVIEMBRE/10141 - 7 DE NOVIEMBRE/10141 - 7 DE NOVIEMBRE</t>
+        </is>
+      </c>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -16165,6 +18085,16 @@
       </c>
       <c r="S193" t="inlineStr">
         <is>
+          <t>10141 - 7 DE NOVIEMBRE/10141 - 7 DE NOVIEMBRE/10141 - 7 DE NOVIEMBRE</t>
+        </is>
+      </c>
+      <c r="T193" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -16246,6 +18176,16 @@
       </c>
       <c r="S194" t="inlineStr">
         <is>
+          <t>10781 CRISTO REDENTOR/10781 CRISTO REDENTOR/10781 CRISTO REDENTOR</t>
+        </is>
+      </c>
+      <c r="T194" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -16327,6 +18267,16 @@
       </c>
       <c r="S195" t="inlineStr">
         <is>
+          <t>10888 SEÑOR DE LOS MILAGROS/10888 SEÑOR DE LOS MILAGROS/10888 SEÑOR DE LOS MILAGROS</t>
+        </is>
+      </c>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -16408,6 +18358,16 @@
       </c>
       <c r="S196" t="inlineStr">
         <is>
+          <t>10992 ANDRES AVELINO CACERES</t>
+        </is>
+      </c>
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -16489,6 +18449,16 @@
       </c>
       <c r="S197" t="inlineStr">
         <is>
+          <t>11130 ARACELY QUISPE NEIRA/11130 ARACELY QUISPE NEIRA/11130 ARACELY QUISPE NEIRA</t>
+        </is>
+      </c>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U197" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -16570,6 +18540,16 @@
       </c>
       <c r="S198" t="inlineStr">
         <is>
+          <t>10175 CONSAGRADA INMACULADA VIRGEN MARIA/10175 CONSAGRADA INMACULADA VIRGEN MARIA</t>
+        </is>
+      </c>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -16651,6 +18631,16 @@
       </c>
       <c r="S199" t="inlineStr">
         <is>
+          <t>10192 JESUS DEL GRAN PODER</t>
+        </is>
+      </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -16732,6 +18722,16 @@
       </c>
       <c r="S200" t="inlineStr">
         <is>
+          <t>10783/10783</t>
+        </is>
+      </c>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -16813,6 +18813,16 @@
       </c>
       <c r="S201" t="inlineStr">
         <is>
+          <t>10182/10182</t>
+        </is>
+      </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -16894,6 +18904,16 @@
       </c>
       <c r="S202" t="inlineStr">
         <is>
+          <t>10182/10182</t>
+        </is>
+      </c>
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U202" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -16975,6 +18995,16 @@
       </c>
       <c r="S203" t="inlineStr">
         <is>
+          <t>11095 SAN IGNACIO DE LOYOLA</t>
+        </is>
+      </c>
+      <c r="T203" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -17056,6 +19086,16 @@
       </c>
       <c r="S204" t="inlineStr">
         <is>
+          <t>11264</t>
+        </is>
+      </c>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -17137,6 +19177,16 @@
       </c>
       <c r="S205" t="inlineStr">
         <is>
+          <t>10906 JOSE MARIA EGUREN/10906 JOSE MARIA EGUREN</t>
+        </is>
+      </c>
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -17218,6 +19268,16 @@
       </c>
       <c r="S206" t="inlineStr">
         <is>
+          <t>60536/60536</t>
+        </is>
+      </c>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -17297,6 +19357,16 @@
       </c>
       <c r="S207" t="inlineStr">
         <is>
+          <t>60536/60536</t>
+        </is>
+      </c>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -17378,6 +19448,16 @@
       </c>
       <c r="S208" t="inlineStr">
         <is>
+          <t>60695 NUESTRA SEÑORA DE AMAZONAS/60695 NUESTRA SEÑORA DE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="T208" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U208" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -17457,6 +19537,16 @@
       </c>
       <c r="S209" t="inlineStr">
         <is>
+          <t>60695 NUESTRA SEÑORA DE AMAZONAS/60695 NUESTRA SEÑORA DE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="T209" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -17538,6 +19628,16 @@
       </c>
       <c r="S210" t="inlineStr">
         <is>
+          <t>60618 DIVINO NIÑO JESUS/60618 DIVINO NIÑO JESUS</t>
+        </is>
+      </c>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U210" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -17617,6 +19717,16 @@
       </c>
       <c r="S211" t="inlineStr">
         <is>
+          <t>60618 DIVINO NIÑO JESUS/60618 DIVINO NIÑO JESUS</t>
+        </is>
+      </c>
+      <c r="T211" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -17698,6 +19808,16 @@
       </c>
       <c r="S212" t="inlineStr">
         <is>
+          <t>60740 VICTORIA ABAD CORREA/60740 VICTORIA ABAD CORREA</t>
+        </is>
+      </c>
+      <c r="T212" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -17777,6 +19897,16 @@
       </c>
       <c r="S213" t="inlineStr">
         <is>
+          <t>60740 VICTORIA ABAD CORREA/60740 VICTORIA ABAD CORREA</t>
+        </is>
+      </c>
+      <c r="T213" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -17858,6 +19988,16 @@
       </c>
       <c r="S214" t="inlineStr">
         <is>
+          <t>60740 VICTORIA ABAD CORREA/60740 VICTORIA ABAD CORREA</t>
+        </is>
+      </c>
+      <c r="T214" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U214" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -17939,6 +20079,16 @@
       </c>
       <c r="S215" t="inlineStr">
         <is>
+          <t>189 NIÑO JESUS</t>
+        </is>
+      </c>
+      <c r="T215" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -18020,6 +20170,16 @@
       </c>
       <c r="S216" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="T216" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U216" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -18101,6 +20261,16 @@
       </c>
       <c r="S217" t="inlineStr">
         <is>
+          <t>11613 NARCISA LANDAZURI DE JESUS/11613 NARCISA LANDAZURI DE JESUS</t>
+        </is>
+      </c>
+      <c r="T217" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -18182,6 +20352,16 @@
       </c>
       <c r="S218" t="inlineStr">
         <is>
+          <t>11606 VIRGEN DE CORTES/11606 VIRGEN DE CORTES</t>
+        </is>
+      </c>
+      <c r="T218" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U218" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -18263,6 +20443,16 @@
       </c>
       <c r="S219" t="inlineStr">
         <is>
+          <t>397</t>
+        </is>
+      </c>
+      <c r="T219" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U219" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -18344,6 +20534,16 @@
       </c>
       <c r="S220" t="inlineStr">
         <is>
+          <t>424 FRANCISCO I</t>
+        </is>
+      </c>
+      <c r="T220" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -18425,6 +20625,16 @@
       </c>
       <c r="S221" t="inlineStr">
         <is>
+          <t>11636 JEAN PIAGET/11636 JEAN PIAGET</t>
+        </is>
+      </c>
+      <c r="T221" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -18506,6 +20716,16 @@
       </c>
       <c r="S222" t="inlineStr">
         <is>
+          <t>FRANCISCA MARIA RUIZ VILLAR/FRANCISCA MARIA RUIZ VILLAR/FRANCISCA MARIA RUIZ VILLAR</t>
+        </is>
+      </c>
+      <c r="T222" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -18587,6 +20807,16 @@
       </c>
       <c r="S223" t="inlineStr">
         <is>
+          <t>11611 ROSA MERINO</t>
+        </is>
+      </c>
+      <c r="T223" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -18668,6 +20898,16 @@
       </c>
       <c r="S224" t="inlineStr">
         <is>
+          <t>11632 SAN JUAN BAUTISTA</t>
+        </is>
+      </c>
+      <c r="T224" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -18749,6 +20989,16 @@
       </c>
       <c r="S225" t="inlineStr">
         <is>
+          <t>601584</t>
+        </is>
+      </c>
+      <c r="T225" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -18828,6 +21078,16 @@
       </c>
       <c r="S226" t="inlineStr">
         <is>
+          <t>601584</t>
+        </is>
+      </c>
+      <c r="T226" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -18909,6 +21169,16 @@
       </c>
       <c r="S227" t="inlineStr">
         <is>
+          <t>480 SANTA TERESITA DE JESUS</t>
+        </is>
+      </c>
+      <c r="T227" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U227" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -18990,6 +21260,16 @@
       </c>
       <c r="S228" t="inlineStr">
         <is>
+          <t>60784 JOSE JAVIER GARCIA OLORTEGUI/60784 JOSE JAVIER GARCIA OLORTEGUI</t>
+        </is>
+      </c>
+      <c r="T228" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U228" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -19069,6 +21349,16 @@
       </c>
       <c r="S229" t="inlineStr">
         <is>
+          <t>60784 JOSE JAVIER GARCIA OLORTEGUI/60784 JOSE JAVIER GARCIA OLORTEGUI</t>
+        </is>
+      </c>
+      <c r="T229" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U229" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -19150,6 +21440,16 @@
       </c>
       <c r="S230" t="inlineStr">
         <is>
+          <t>10207 JOSE JUSTO ARCE GONZALES</t>
+        </is>
+      </c>
+      <c r="T230" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -19231,6 +21531,16 @@
       </c>
       <c r="S231" t="inlineStr">
         <is>
+          <t>10941 SAN RICARDO PAMPURI</t>
+        </is>
+      </c>
+      <c r="T231" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -19312,6 +21622,16 @@
       </c>
       <c r="S232" t="inlineStr">
         <is>
+          <t>10172 MARIA ISABEL NUÑEZ FLORES DE SILVA/10172 MARIA ISABEL NUÑEZ FLORES DE SILVA</t>
+        </is>
+      </c>
+      <c r="T232" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -19397,6 +21717,16 @@
       </c>
       <c r="S233" t="inlineStr">
         <is>
+          <t>3037 GRAN AMAUTA/3037 GRAN AMAUTA/3037 GRAN AMAUTA/3037 GRAN AMAUTA</t>
+        </is>
+      </c>
+      <c r="T233" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -19482,6 +21812,16 @@
       </c>
       <c r="S234" t="inlineStr">
         <is>
+          <t>3037 GRAN AMAUTA/3037 GRAN AMAUTA/3037 GRAN AMAUTA/3037 GRAN AMAUTA</t>
+        </is>
+      </c>
+      <c r="T234" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U234" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -19567,6 +21907,16 @@
       </c>
       <c r="S235" t="inlineStr">
         <is>
+          <t>14376 LUIS MIGUEL SANCHEZ CERRO/14376 LUIS MIGUEL SANCHEZ CERRO/14376 LUIS MIGUEL SANCHEZ CERRO</t>
+        </is>
+      </c>
+      <c r="T235" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U235" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -19648,6 +21998,16 @@
       </c>
       <c r="S236" t="inlineStr">
         <is>
+          <t>10198 SAN MARTIN DE PORRAS/10198 SAN MARTIN DE PORRAS</t>
+        </is>
+      </c>
+      <c r="T236" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U236" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -19729,6 +22089,16 @@
       </c>
       <c r="S237" t="inlineStr">
         <is>
+          <t>60208/60208</t>
+        </is>
+      </c>
+      <c r="T237" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U237" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -19808,6 +22178,16 @@
       </c>
       <c r="S238" t="inlineStr">
         <is>
+          <t>60208/60208</t>
+        </is>
+      </c>
+      <c r="T238" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U238" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -19889,6 +22269,16 @@
       </c>
       <c r="S239" t="inlineStr">
         <is>
+          <t>62321</t>
+        </is>
+      </c>
+      <c r="T239" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U239" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -19968,6 +22358,16 @@
       </c>
       <c r="S240" t="inlineStr">
         <is>
+          <t>62321</t>
+        </is>
+      </c>
+      <c r="T240" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U240" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -20049,6 +22449,16 @@
       </c>
       <c r="S241" t="inlineStr">
         <is>
+          <t>451</t>
+        </is>
+      </c>
+      <c r="T241" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U241" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -20130,6 +22540,16 @@
       </c>
       <c r="S242" t="inlineStr">
         <is>
+          <t>TUNA</t>
+        </is>
+      </c>
+      <c r="T242" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U242" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -20209,6 +22629,16 @@
       </c>
       <c r="S243" t="inlineStr">
         <is>
+          <t>TUNA</t>
+        </is>
+      </c>
+      <c r="T243" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U243" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -20290,6 +22720,16 @@
       </c>
       <c r="S244" t="inlineStr">
         <is>
+          <t>522 CLORINDA MATTO DE TURNER</t>
+        </is>
+      </c>
+      <c r="T244" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U244" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -20371,6 +22811,16 @@
       </c>
       <c r="S245" t="inlineStr">
         <is>
+          <t>10174 VIRGEN DE LA DIVINA PROVIDENCIA</t>
+        </is>
+      </c>
+      <c r="T245" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U245" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -20452,6 +22902,16 @@
       </c>
       <c r="S246" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="T246" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U246" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -20533,6 +22993,16 @@
       </c>
       <c r="S247" t="inlineStr">
         <is>
+          <t>PALMICHE</t>
+        </is>
+      </c>
+      <c r="T247" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U247" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -20612,6 +23082,16 @@
       </c>
       <c r="S248" t="inlineStr">
         <is>
+          <t>PALMICHE</t>
+        </is>
+      </c>
+      <c r="T248" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U248" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -20693,6 +23173,16 @@
       </c>
       <c r="S249" t="inlineStr">
         <is>
+          <t>62328 JUAN DANIEL DEL AGUILA VELASQUEZ/JUAN DANIEL DEL AGUILA VELASQUEZ/62328 JUAN DANIEL DEL AGUILA VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="T249" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U249" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -20772,6 +23262,16 @@
       </c>
       <c r="S250" t="inlineStr">
         <is>
+          <t>62328 JUAN DANIEL DEL AGUILA VELASQUEZ/JUAN DANIEL DEL AGUILA VELASQUEZ/62328 JUAN DANIEL DEL AGUILA VELASQUEZ</t>
+        </is>
+      </c>
+      <c r="T250" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U250" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -20853,6 +23353,16 @@
       </c>
       <c r="S251" t="inlineStr">
         <is>
+          <t>62345/62345/62345</t>
+        </is>
+      </c>
+      <c r="T251" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U251" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -20934,6 +23444,16 @@
       </c>
       <c r="S252" t="inlineStr">
         <is>
+          <t>62345/62345/62345</t>
+        </is>
+      </c>
+      <c r="T252" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U252" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -21013,6 +23533,16 @@
       </c>
       <c r="S253" t="inlineStr">
         <is>
+          <t>62345/62345/62345</t>
+        </is>
+      </c>
+      <c r="T253" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U253" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -21094,6 +23624,16 @@
       </c>
       <c r="S254" t="inlineStr">
         <is>
+          <t>ARAHUANTE</t>
+        </is>
+      </c>
+      <c r="T254" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U254" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -21173,6 +23713,16 @@
       </c>
       <c r="S255" t="inlineStr">
         <is>
+          <t>ARAHUANTE</t>
+        </is>
+      </c>
+      <c r="T255" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U255" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -21254,6 +23804,16 @@
       </c>
       <c r="S256" t="inlineStr">
         <is>
+          <t>62261 ATAHUALPA</t>
+        </is>
+      </c>
+      <c r="T256" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U256" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -21333,6 +23893,16 @@
       </c>
       <c r="S257" t="inlineStr">
         <is>
+          <t>62261 ATAHUALPA</t>
+        </is>
+      </c>
+      <c r="T257" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U257" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -21414,6 +23984,16 @@
       </c>
       <c r="S258" t="inlineStr">
         <is>
+          <t>EL TALLAN/EL TALLAN/EL TALLAN</t>
+        </is>
+      </c>
+      <c r="T258" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U258" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -21495,6 +24075,16 @@
       </c>
       <c r="S259" t="inlineStr">
         <is>
+          <t>GENERAL JUAN VELASCO ALVARADO/GENERAL JUAN VELASCO ALVARADO/GENERAL JUAN VELASCO ALVARADO</t>
+        </is>
+      </c>
+      <c r="T259" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U259" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -21576,6 +24166,16 @@
       </c>
       <c r="S260" t="inlineStr">
         <is>
+          <t>GENERAL JUAN VELASCO ALVARADO/GENERAL JUAN VELASCO ALVARADO/GENERAL JUAN VELASCO ALVARADO</t>
+        </is>
+      </c>
+      <c r="T260" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U260" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -21657,6 +24257,16 @@
       </c>
       <c r="S261" t="inlineStr">
         <is>
+          <t>GENERAL JUAN VELASCO ALVARADO/GENERAL JUAN VELASCO ALVARADO/GENERAL JUAN VELASCO ALVARADO</t>
+        </is>
+      </c>
+      <c r="T261" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U261" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -21738,6 +24348,16 @@
       </c>
       <c r="S262" t="inlineStr">
         <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="T262" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U262" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -21819,6 +24439,16 @@
       </c>
       <c r="S263" t="inlineStr">
         <is>
+          <t>360 SAN MARTIN DE PORRES</t>
+        </is>
+      </c>
+      <c r="T263" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U263" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -21900,6 +24530,16 @@
       </c>
       <c r="S264" t="inlineStr">
         <is>
+          <t>757</t>
+        </is>
+      </c>
+      <c r="T264" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U264" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -21981,6 +24621,16 @@
       </c>
       <c r="S265" t="inlineStr">
         <is>
+          <t>14920 ALMIRANTE MIGUEL GRAU/14920 ALMIRANTE MIGUEL GRAU</t>
+        </is>
+      </c>
+      <c r="T265" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U265" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -22062,6 +24712,16 @@
       </c>
       <c r="S266" t="inlineStr">
         <is>
+          <t>15018 CORONEL ANDRES RAZURI/15018 CORONEL ANDRES RAZURI/15018 CORONEL ANDRES RAZURI</t>
+        </is>
+      </c>
+      <c r="T266" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U266" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -22143,6 +24803,16 @@
       </c>
       <c r="S267" t="inlineStr">
         <is>
+          <t>15176</t>
+        </is>
+      </c>
+      <c r="T267" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U267" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -22224,6 +24894,16 @@
       </c>
       <c r="S268" t="inlineStr">
         <is>
+          <t>CIRO ALEGRIA</t>
+        </is>
+      </c>
+      <c r="T268" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U268" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -22305,6 +24985,16 @@
       </c>
       <c r="S269" t="inlineStr">
         <is>
+          <t>14873</t>
+        </is>
+      </c>
+      <c r="T269" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U269" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -22386,6 +25076,16 @@
       </c>
       <c r="S270" t="inlineStr">
         <is>
+          <t>0363/0363</t>
+        </is>
+      </c>
+      <c r="T270" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U270" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -22465,6 +25165,16 @@
       </c>
       <c r="S271" t="inlineStr">
         <is>
+          <t>0363/0363</t>
+        </is>
+      </c>
+      <c r="T271" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U271" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -22546,6 +25256,16 @@
       </c>
       <c r="S272" t="inlineStr">
         <is>
+          <t>0092</t>
+        </is>
+      </c>
+      <c r="T272" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U272" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -22627,6 +25347,16 @@
       </c>
       <c r="S273" t="inlineStr">
         <is>
+          <t>0673</t>
+        </is>
+      </c>
+      <c r="T273" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U273" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -22706,6 +25436,16 @@
       </c>
       <c r="S274" t="inlineStr">
         <is>
+          <t>0673</t>
+        </is>
+      </c>
+      <c r="T274" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U274" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -22787,6 +25527,16 @@
       </c>
       <c r="S275" t="inlineStr">
         <is>
+          <t>0726/0726</t>
+        </is>
+      </c>
+      <c r="T275" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U275" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -22866,6 +25616,16 @@
       </c>
       <c r="S276" t="inlineStr">
         <is>
+          <t>0726/0726</t>
+        </is>
+      </c>
+      <c r="T276" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U276" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -22947,6 +25707,16 @@
       </c>
       <c r="S277" t="inlineStr">
         <is>
+          <t>0726/0726</t>
+        </is>
+      </c>
+      <c r="T277" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U277" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -23028,6 +25798,16 @@
       </c>
       <c r="S278" t="inlineStr">
         <is>
+          <t>62716</t>
+        </is>
+      </c>
+      <c r="T278" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U278" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -23107,6 +25887,16 @@
       </c>
       <c r="S279" t="inlineStr">
         <is>
+          <t>62716</t>
+        </is>
+      </c>
+      <c r="T279" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U279" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -23188,6 +25978,16 @@
       </c>
       <c r="S280" t="inlineStr">
         <is>
+          <t>62348/62348</t>
+        </is>
+      </c>
+      <c r="T280" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U280" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -23267,6 +26067,16 @@
       </c>
       <c r="S281" t="inlineStr">
         <is>
+          <t>62348/62348</t>
+        </is>
+      </c>
+      <c r="T281" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U281" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -23348,6 +26158,16 @@
       </c>
       <c r="S282" t="inlineStr">
         <is>
+          <t>1311</t>
+        </is>
+      </c>
+      <c r="T282" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U282" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -23429,6 +26249,16 @@
       </c>
       <c r="S283" t="inlineStr">
         <is>
+          <t>1412</t>
+        </is>
+      </c>
+      <c r="T283" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U283" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -23508,6 +26338,16 @@
       </c>
       <c r="S284" t="inlineStr">
         <is>
+          <t>0650/0650</t>
+        </is>
+      </c>
+      <c r="T284" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U284" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -23589,6 +26429,16 @@
       </c>
       <c r="S285" t="inlineStr">
         <is>
+          <t>0640/0640</t>
+        </is>
+      </c>
+      <c r="T285" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U285" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -23668,6 +26518,16 @@
       </c>
       <c r="S286" t="inlineStr">
         <is>
+          <t>0640/0640</t>
+        </is>
+      </c>
+      <c r="T286" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U286" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -23749,6 +26609,16 @@
       </c>
       <c r="S287" t="inlineStr">
         <is>
+          <t>0646/0646</t>
+        </is>
+      </c>
+      <c r="T287" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U287" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -23828,6 +26698,16 @@
       </c>
       <c r="S288" t="inlineStr">
         <is>
+          <t>0646/0646</t>
+        </is>
+      </c>
+      <c r="T288" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U288" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -23909,6 +26789,16 @@
       </c>
       <c r="S289" t="inlineStr">
         <is>
+          <t>721</t>
+        </is>
+      </c>
+      <c r="T289" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U289" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -23990,6 +26880,16 @@
       </c>
       <c r="S290" t="inlineStr">
         <is>
+          <t>8 DE DICIEMBRE/8 DE DICIEMBRE/8 DE DICIEMBRE</t>
+        </is>
+      </c>
+      <c r="T290" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U290" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -24071,6 +26971,16 @@
       </c>
       <c r="S291" t="inlineStr">
         <is>
+          <t>15071/15071</t>
+        </is>
+      </c>
+      <c r="T291" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U291" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -24156,6 +27066,16 @@
       </c>
       <c r="S292" t="inlineStr">
         <is>
+          <t>TUPAC AMARU</t>
+        </is>
+      </c>
+      <c r="T292" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U292" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -24241,6 +27161,16 @@
       </c>
       <c r="S293" t="inlineStr">
         <is>
+          <t>11602 RICARDO PALMA/11602 RICARDO PALMA/11602 RICARDO PALMA</t>
+        </is>
+      </c>
+      <c r="T293" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U293" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -24322,6 +27252,16 @@
       </c>
       <c r="S294" t="inlineStr">
         <is>
+          <t>11124 NUESTRA SEÑORA DE LA PAZ/11124 NUESTRA SEÑORA DE LA PAZ</t>
+        </is>
+      </c>
+      <c r="T294" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U294" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -24403,6 +27343,16 @@
       </c>
       <c r="S295" t="inlineStr">
         <is>
+          <t>21559 ANTONIO GRAÑA ELIZALDE/21559 ANTONIO GRAÑA ELIZALDE/21559 ANTONIO GRAÑA ELIZALDE</t>
+        </is>
+      </c>
+      <c r="T295" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U295" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -24484,6 +27434,16 @@
       </c>
       <c r="S296" t="inlineStr">
         <is>
+          <t>15332/15332</t>
+        </is>
+      </c>
+      <c r="T296" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U296" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -24565,6 +27525,16 @@
       </c>
       <c r="S297" t="inlineStr">
         <is>
+          <t>TUPAC AMARU II/TUPAC AMARU II/TUPAC AMARU II</t>
+        </is>
+      </c>
+      <c r="T297" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U297" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -24646,6 +27616,16 @@
       </c>
       <c r="S298" t="inlineStr">
         <is>
+          <t>14506</t>
+        </is>
+      </c>
+      <c r="T298" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U298" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -24727,6 +27707,16 @@
       </c>
       <c r="S299" t="inlineStr">
         <is>
+          <t>PEDRO RUIZ GALLO/PEDRO RUIZ GALLO</t>
+        </is>
+      </c>
+      <c r="T299" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U299" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -24808,6 +27798,16 @@
       </c>
       <c r="S300" t="inlineStr">
         <is>
+          <t>ROSA CARDO DE GUARDERAS/ROSA CARDO DE GUARDERAS/ROSA CARDO DE GUARDERAS</t>
+        </is>
+      </c>
+      <c r="T300" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U300" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -24889,6 +27889,16 @@
       </c>
       <c r="S301" t="inlineStr">
         <is>
+          <t>20507/20507</t>
+        </is>
+      </c>
+      <c r="T301" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U301" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -24970,6 +27980,16 @@
       </c>
       <c r="S302" t="inlineStr">
         <is>
+          <t>TUPAC AMARU/TUPAC AMARU</t>
+        </is>
+      </c>
+      <c r="T302" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U302" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -25051,6 +28071,16 @@
       </c>
       <c r="S303" t="inlineStr">
         <is>
+          <t>TUPAC AMARU/TUPAC AMARU</t>
+        </is>
+      </c>
+      <c r="T303" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U303" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -25132,6 +28162,16 @@
       </c>
       <c r="S304" t="inlineStr">
         <is>
+          <t>032</t>
+        </is>
+      </c>
+      <c r="T304" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U304" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -25213,6 +28253,16 @@
       </c>
       <c r="S305" t="inlineStr">
         <is>
+          <t>038 SANTOS MAXIMINA MOGOLLON ALVARADO/038 SANTOS MAXIMINA MOGOLLON ALVARADO</t>
+        </is>
+      </c>
+      <c r="T305" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U305" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -25294,6 +28344,16 @@
       </c>
       <c r="S306" t="inlineStr">
         <is>
+          <t>114 MERCEDES CORTEZ DE GARCIA</t>
+        </is>
+      </c>
+      <c r="T306" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U306" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -25375,6 +28435,16 @@
       </c>
       <c r="S307" t="inlineStr">
         <is>
+          <t>051 ROSA LOPEZ ITURRALDE</t>
+        </is>
+      </c>
+      <c r="T307" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U307" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -25456,6 +28526,16 @@
       </c>
       <c r="S308" t="inlineStr">
         <is>
+          <t>SAN JUAN DE LA VIRGEN</t>
+        </is>
+      </c>
+      <c r="T308" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U308" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -25537,6 +28617,16 @@
       </c>
       <c r="S309" t="inlineStr">
         <is>
+          <t>062 NIÑOS DE LA PAZ</t>
+        </is>
+      </c>
+      <c r="T309" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U309" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -25618,6 +28708,16 @@
       </c>
       <c r="S310" t="inlineStr">
         <is>
+          <t>ANTONIO RAIMONDI/ANTONIO RAIMONDI</t>
+        </is>
+      </c>
+      <c r="T310" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U310" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -25699,6 +28799,16 @@
       </c>
       <c r="S311" t="inlineStr">
         <is>
+          <t>62551/62551</t>
+        </is>
+      </c>
+      <c r="T311" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U311" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -25778,6 +28888,16 @@
       </c>
       <c r="S312" t="inlineStr">
         <is>
+          <t>62551/62551</t>
+        </is>
+      </c>
+      <c r="T312" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U312" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -25859,6 +28979,16 @@
       </c>
       <c r="S313" t="inlineStr">
         <is>
+          <t>1032</t>
+        </is>
+      </c>
+      <c r="T313" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U313" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -25940,6 +29070,16 @@
       </c>
       <c r="S314" t="inlineStr">
         <is>
+          <t>1150</t>
+        </is>
+      </c>
+      <c r="T314" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U314" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -26021,6 +29161,16 @@
       </c>
       <c r="S315" t="inlineStr">
         <is>
+          <t>62807 CESAR VALLEJO</t>
+        </is>
+      </c>
+      <c r="T315" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U315" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -26100,6 +29250,16 @@
       </c>
       <c r="S316" t="inlineStr">
         <is>
+          <t>62807 CESAR VALLEJO</t>
+        </is>
+      </c>
+      <c r="T316" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U316" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -26181,6 +29341,16 @@
       </c>
       <c r="S317" t="inlineStr">
         <is>
+          <t>PEQUEÑOS GENIOS</t>
+        </is>
+      </c>
+      <c r="T317" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U317" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -26262,6 +29432,16 @@
       </c>
       <c r="S318" t="inlineStr">
         <is>
+          <t>511 VIRGEN DE GUADALUPE</t>
+        </is>
+      </c>
+      <c r="T318" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U318" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -26343,6 +29523,16 @@
       </c>
       <c r="S319" t="inlineStr">
         <is>
+          <t>LA CABAÑA DEL SABER</t>
+        </is>
+      </c>
+      <c r="T319" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U319" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -26424,6 +29614,16 @@
       </c>
       <c r="S320" t="inlineStr">
         <is>
+          <t>62352</t>
+        </is>
+      </c>
+      <c r="T320" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U320" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -26503,6 +29703,16 @@
       </c>
       <c r="S321" t="inlineStr">
         <is>
+          <t>62352</t>
+        </is>
+      </c>
+      <c r="T321" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U321" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -26584,6 +29794,16 @@
       </c>
       <c r="S322" t="inlineStr">
         <is>
+          <t>15240/15240</t>
+        </is>
+      </c>
+      <c r="T322" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U322" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -26665,6 +29885,16 @@
       </c>
       <c r="S323" t="inlineStr">
         <is>
+          <t>1509</t>
+        </is>
+      </c>
+      <c r="T323" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U323" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -26746,6 +29976,16 @@
       </c>
       <c r="S324" t="inlineStr">
         <is>
+          <t>101 CAP. FAP JOSE ABELARDO QUIÑONES GONZALES/101 CAP. FAP JOSE ABELARDO QUIÑONES GONZALES</t>
+        </is>
+      </c>
+      <c r="T324" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U324" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -26827,6 +30067,16 @@
       </c>
       <c r="S325" t="inlineStr">
         <is>
+          <t>ANATOLIO POLO GRADOS/ANATOLIO POLO GRADOS</t>
+        </is>
+      </c>
+      <c r="T325" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U325" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -26908,6 +30158,16 @@
       </c>
       <c r="S326" t="inlineStr">
         <is>
+          <t>ANATOLIO POLO GRADOS/ANATOLIO POLO GRADOS</t>
+        </is>
+      </c>
+      <c r="T326" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U326" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -26989,6 +30249,16 @@
       </c>
       <c r="S327" t="inlineStr">
         <is>
+          <t>20401/20401</t>
+        </is>
+      </c>
+      <c r="T327" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U327" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -27074,6 +30344,16 @@
       </c>
       <c r="S328" t="inlineStr">
         <is>
+          <t>20442/20442/20442</t>
+        </is>
+      </c>
+      <c r="T328" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U328" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -27155,6 +30435,16 @@
       </c>
       <c r="S329" t="inlineStr">
         <is>
+          <t>LAS DELICIAS</t>
+        </is>
+      </c>
+      <c r="T329" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U329" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -27240,6 +30530,16 @@
       </c>
       <c r="S330" t="inlineStr">
         <is>
+          <t>10813 SANTA ROSA DE LIMA</t>
+        </is>
+      </c>
+      <c r="T330" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U330" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -27325,6 +30625,16 @@
       </c>
       <c r="S331" t="inlineStr">
         <is>
+          <t>10240</t>
+        </is>
+      </c>
+      <c r="T331" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U331" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -27410,6 +30720,16 @@
       </c>
       <c r="S332" t="inlineStr">
         <is>
+          <t>11521 MARIA DE LOURDES/11521 MARIA DE LOURDES/11521 MARIA DE LOURDES</t>
+        </is>
+      </c>
+      <c r="T332" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U332" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -27495,6 +30815,16 @@
       </c>
       <c r="S333" t="inlineStr">
         <is>
+          <t>11607</t>
+        </is>
+      </c>
+      <c r="T333" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U333" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -27574,6 +30904,16 @@
       </c>
       <c r="S334" t="inlineStr">
         <is>
+          <t>16312</t>
+        </is>
+      </c>
+      <c r="T334" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U334" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -27653,6 +30993,16 @@
       </c>
       <c r="S335" t="inlineStr">
         <is>
+          <t>WEEPIU YUU KUYU</t>
+        </is>
+      </c>
+      <c r="T335" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U335" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -27738,6 +31088,16 @@
       </c>
       <c r="S336" t="inlineStr">
         <is>
+          <t>004/004</t>
+        </is>
+      </c>
+      <c r="T336" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U336" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -27823,6 +31183,16 @@
       </c>
       <c r="S337" t="inlineStr">
         <is>
+          <t>ALBERTO PALLETE/ALBERTO PALLETE/ALBERTO PALLETE</t>
+        </is>
+      </c>
+      <c r="T337" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U337" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -27902,6 +31272,16 @@
       </c>
       <c r="S338" t="inlineStr">
         <is>
+          <t>16309/16309</t>
+        </is>
+      </c>
+      <c r="T338" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U338" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -27981,6 +31361,16 @@
       </c>
       <c r="S339" t="inlineStr">
         <is>
+          <t>16654</t>
+        </is>
+      </c>
+      <c r="T339" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U339" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -28060,6 +31450,16 @@
       </c>
       <c r="S340" t="inlineStr">
         <is>
+          <t>16303</t>
+        </is>
+      </c>
+      <c r="T340" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U340" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -28139,6 +31539,16 @@
       </c>
       <c r="S341" t="inlineStr">
         <is>
+          <t>16705</t>
+        </is>
+      </c>
+      <c r="T341" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U341" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -28218,6 +31628,16 @@
       </c>
       <c r="S342" t="inlineStr">
         <is>
+          <t>DIONISIO MANCO CAMPOS/DIONISIO MANCO CAMPOS/DIONISIO MANCO CAMPOS</t>
+        </is>
+      </c>
+      <c r="T342" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U342" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -28303,6 +31723,16 @@
       </c>
       <c r="S343" t="inlineStr">
         <is>
+          <t>BASILIO AUQUI</t>
+        </is>
+      </c>
+      <c r="T343" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U343" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -28388,6 +31818,16 @@
       </c>
       <c r="S344" t="inlineStr">
         <is>
+          <t>BASILIO AUQUI</t>
+        </is>
+      </c>
+      <c r="T344" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U344" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -28473,6 +31913,16 @@
       </c>
       <c r="S345" t="inlineStr">
         <is>
+          <t>BASILIO AUQUI</t>
+        </is>
+      </c>
+      <c r="T345" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U345" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -28554,6 +32004,16 @@
       </c>
       <c r="S346" t="inlineStr">
         <is>
+          <t>15499/15499</t>
+        </is>
+      </c>
+      <c r="T346" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U346" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -28635,6 +32095,16 @@
       </c>
       <c r="S347" t="inlineStr">
         <is>
+          <t>AREAS TECNICAS/AREAS TECNICAS</t>
+        </is>
+      </c>
+      <c r="T347" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U347" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -28716,6 +32186,16 @@
       </c>
       <c r="S348" t="inlineStr">
         <is>
+          <t>SAN AGUSTIN</t>
+        </is>
+      </c>
+      <c r="T348" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U348" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -28797,6 +32277,16 @@
       </c>
       <c r="S349" t="inlineStr">
         <is>
+          <t>1459</t>
+        </is>
+      </c>
+      <c r="T349" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U349" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -28878,6 +32368,16 @@
       </c>
       <c r="S350" t="inlineStr">
         <is>
+          <t>14093 ABRAHAM RUIZ NUNURA/14093 ABRAHAM RUIZ NUNURA/14093 ABRAHAM RUIZ NUNURA</t>
+        </is>
+      </c>
+      <c r="T350" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U350" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -28959,6 +32459,16 @@
       </c>
       <c r="S351" t="inlineStr">
         <is>
+          <t>14093 ABRAHAM RUIZ NUNURA/14093 ABRAHAM RUIZ NUNURA/14093 ABRAHAM RUIZ NUNURA</t>
+        </is>
+      </c>
+      <c r="T351" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U351" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -29040,6 +32550,16 @@
       </c>
       <c r="S352" t="inlineStr">
         <is>
+          <t>14948</t>
+        </is>
+      </c>
+      <c r="T352" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U352" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -29121,6 +32641,16 @@
       </c>
       <c r="S353" t="inlineStr">
         <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="T353" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U353" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -29202,6 +32732,16 @@
       </c>
       <c r="S354" t="inlineStr">
         <is>
+          <t>20442/20442/20442</t>
+        </is>
+      </c>
+      <c r="T354" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U354" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -29283,6 +32823,16 @@
       </c>
       <c r="S355" t="inlineStr">
         <is>
+          <t>392</t>
+        </is>
+      </c>
+      <c r="T355" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U355" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -29364,6 +32914,16 @@
       </c>
       <c r="S356" t="inlineStr">
         <is>
+          <t>20858</t>
+        </is>
+      </c>
+      <c r="T356" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U356" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -29449,6 +33009,16 @@
       </c>
       <c r="S357" t="inlineStr">
         <is>
+          <t>11504/11504</t>
+        </is>
+      </c>
+      <c r="T357" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U357" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -29534,6 +33104,16 @@
       </c>
       <c r="S358" t="inlineStr">
         <is>
+          <t>SAN JUAN BOSCO/SAN JUAN BOSCO</t>
+        </is>
+      </c>
+      <c r="T358" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U358" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -29615,6 +33195,16 @@
       </c>
       <c r="S359" t="inlineStr">
         <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="T359" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U359" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -29696,6 +33286,16 @@
       </c>
       <c r="S360" t="inlineStr">
         <is>
+          <t>86888 SAN MIGUEL ARCANGEL/86888 SAN MIGUEL ARCANGEL/86888 SAN MIGUEL ARCANGEL</t>
+        </is>
+      </c>
+      <c r="T360" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U360" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -29777,6 +33377,16 @@
       </c>
       <c r="S361" t="inlineStr">
         <is>
+          <t>24278 MARIA MENDOZA GUZMAN</t>
+        </is>
+      </c>
+      <c r="T361" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U361" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -29858,6 +33468,16 @@
       </c>
       <c r="S362" t="inlineStr">
         <is>
+          <t>82875</t>
+        </is>
+      </c>
+      <c r="T362" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U362" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -29939,6 +33559,16 @@
       </c>
       <c r="S363" t="inlineStr">
         <is>
+          <t>17511</t>
+        </is>
+      </c>
+      <c r="T363" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U363" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -30020,6 +33650,16 @@
       </c>
       <c r="S364" t="inlineStr">
         <is>
+          <t>16006 CRISTO REY/16006 CRISTO REY</t>
+        </is>
+      </c>
+      <c r="T364" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U364" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -30101,6 +33741,16 @@
       </c>
       <c r="S365" t="inlineStr">
         <is>
+          <t>16006 CRISTO REY/16006 CRISTO REY</t>
+        </is>
+      </c>
+      <c r="T365" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U365" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -30182,6 +33832,16 @@
       </c>
       <c r="S366" t="inlineStr">
         <is>
+          <t>17500</t>
+        </is>
+      </c>
+      <c r="T366" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U366" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -30263,6 +33923,16 @@
       </c>
       <c r="S367" t="inlineStr">
         <is>
+          <t>10662</t>
+        </is>
+      </c>
+      <c r="T367" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U367" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -30344,6 +34014,16 @@
       </c>
       <c r="S368" t="inlineStr">
         <is>
+          <t>32125</t>
+        </is>
+      </c>
+      <c r="T368" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U368" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -30425,6 +34105,16 @@
       </c>
       <c r="S369" t="inlineStr">
         <is>
+          <t>22533 ANTONIA MORENO DE CACERES</t>
+        </is>
+      </c>
+      <c r="T369" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U369" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -30506,6 +34196,16 @@
       </c>
       <c r="S370" t="inlineStr">
         <is>
+          <t>ANTONIA MORENO DE CACERES</t>
+        </is>
+      </c>
+      <c r="T370" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U370" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -30587,6 +34287,16 @@
       </c>
       <c r="S371" t="inlineStr">
         <is>
+          <t>519/22334</t>
+        </is>
+      </c>
+      <c r="T371" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U371" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -30668,6 +34378,16 @@
       </c>
       <c r="S372" t="inlineStr">
         <is>
+          <t>22393/22393</t>
+        </is>
+      </c>
+      <c r="T372" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U372" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -30749,6 +34469,16 @@
       </c>
       <c r="S373" t="inlineStr">
         <is>
+          <t>22730/22730</t>
+        </is>
+      </c>
+      <c r="T373" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U373" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -30830,6 +34560,16 @@
       </c>
       <c r="S374" t="inlineStr">
         <is>
+          <t>22560 MARIA PARADO DE BELLIDO/22560 MARIA PARADO DE BELLIDO</t>
+        </is>
+      </c>
+      <c r="T374" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U374" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -30911,6 +34651,16 @@
       </c>
       <c r="S375" t="inlineStr">
         <is>
+          <t>JOSE DE SAN MARTIN/JOSE DE SAN MARTIN/JOSE DE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="T375" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U375" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -30992,6 +34742,16 @@
       </c>
       <c r="S376" t="inlineStr">
         <is>
+          <t>64441/64441</t>
+        </is>
+      </c>
+      <c r="T376" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U376" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -31072,6 +34832,16 @@
         </is>
       </c>
       <c r="S377" t="inlineStr">
+        <is>
+          <t>31266/31266/31266</t>
+        </is>
+      </c>
+      <c r="T377" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U377" t="inlineStr">
         <is>
           <t>UGME</t>
         </is>
@@ -31124,7 +34894,9 @@
       <c r="P378" t="inlineStr"/>
       <c r="Q378" t="inlineStr"/>
       <c r="R378" t="inlineStr"/>
-      <c r="S378" t="inlineStr">
+      <c r="S378" t="inlineStr"/>
+      <c r="T378" t="inlineStr"/>
+      <c r="U378" t="inlineStr">
         <is>
           <t>UGME</t>
         </is>
@@ -31207,6 +34979,16 @@
       </c>
       <c r="S379" t="inlineStr">
         <is>
+          <t>30736</t>
+        </is>
+      </c>
+      <c r="T379" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U379" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -31288,6 +35070,16 @@
       </c>
       <c r="S380" t="inlineStr">
         <is>
+          <t>30824 EDUARDO FALK LAMPRECHT/30824 EDUARDO FALK LAMPRECHT</t>
+        </is>
+      </c>
+      <c r="T380" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U380" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -31369,6 +35161,16 @@
       </c>
       <c r="S381" t="inlineStr">
         <is>
+          <t>80867 SAGRADO CORAZON DE JESUS/80867 SAGRADO CORAZON DE JESUS</t>
+        </is>
+      </c>
+      <c r="T381" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U381" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -31450,6 +35252,16 @@
       </c>
       <c r="S382" t="inlineStr">
         <is>
+          <t>80867 SAGRADO CORAZON DE JESUS/80867 SAGRADO CORAZON DE JESUS</t>
+        </is>
+      </c>
+      <c r="T382" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U382" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -31531,6 +35343,16 @@
       </c>
       <c r="S383" t="inlineStr">
         <is>
+          <t>82337/82337</t>
+        </is>
+      </c>
+      <c r="T383" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U383" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -31612,6 +35434,16 @@
       </c>
       <c r="S384" t="inlineStr">
         <is>
+          <t>10841 JOSE CARLOS MARIATEGUI/10841 JOSE CARLOS MARIATEGUI</t>
+        </is>
+      </c>
+      <c r="T384" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U384" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -31693,6 +35525,16 @@
       </c>
       <c r="S385" t="inlineStr">
         <is>
+          <t>11589 JUAN VELASCO ALVARADO/11589 JUAN VELASCO ALVARADO/11589 JUAN VELASCO ALVARADO</t>
+        </is>
+      </c>
+      <c r="T385" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U385" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -31774,6 +35616,16 @@
       </c>
       <c r="S386" t="inlineStr">
         <is>
+          <t>10138 AUGUSTO CASTILLO MURO SIME/10138 AUGUSTO CASTILLO MURO SIME</t>
+        </is>
+      </c>
+      <c r="T386" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U386" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -31855,6 +35707,16 @@
       </c>
       <c r="S387" t="inlineStr">
         <is>
+          <t>11192/11192</t>
+        </is>
+      </c>
+      <c r="T387" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U387" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -31936,6 +35798,16 @@
       </c>
       <c r="S388" t="inlineStr">
         <is>
+          <t>11226</t>
+        </is>
+      </c>
+      <c r="T388" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U388" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -32017,6 +35889,16 @@
       </c>
       <c r="S389" t="inlineStr">
         <is>
+          <t>10194</t>
+        </is>
+      </c>
+      <c r="T389" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U389" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -32098,6 +35980,16 @@
       </c>
       <c r="S390" t="inlineStr">
         <is>
+          <t>11240 ANNA MARIA JARVIS</t>
+        </is>
+      </c>
+      <c r="T390" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U390" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -32179,6 +36071,16 @@
       </c>
       <c r="S391" t="inlineStr">
         <is>
+          <t>10227</t>
+        </is>
+      </c>
+      <c r="T391" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U391" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -32260,6 +36162,16 @@
       </c>
       <c r="S392" t="inlineStr">
         <is>
+          <t>10848 SAPAME LAS SALINAS/10848 SAPAME LAS SALINAS</t>
+        </is>
+      </c>
+      <c r="T392" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U392" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -32341,6 +36253,16 @@
       </c>
       <c r="S393" t="inlineStr">
         <is>
+          <t>11164 LAS PIRAMIDES DE TUCUME</t>
+        </is>
+      </c>
+      <c r="T393" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U393" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -32422,6 +36344,16 @@
       </c>
       <c r="S394" t="inlineStr">
         <is>
+          <t>8167/8167</t>
+        </is>
+      </c>
+      <c r="T394" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U394" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -32503,6 +36435,16 @@
       </c>
       <c r="S395" t="inlineStr">
         <is>
+          <t>AUGUSTO B. LEGUIA/AUGUSTO B. LEGUIA</t>
+        </is>
+      </c>
+      <c r="T395" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U395" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -32584,6 +36526,16 @@
       </c>
       <c r="S396" t="inlineStr">
         <is>
+          <t>20553 JULIO CESAR TELLO ROJAS</t>
+        </is>
+      </c>
+      <c r="T396" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U396" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -32665,6 +36617,16 @@
       </c>
       <c r="S397" t="inlineStr">
         <is>
+          <t>62299/62299</t>
+        </is>
+      </c>
+      <c r="T397" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U397" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -32746,6 +36708,16 @@
       </c>
       <c r="S398" t="inlineStr">
         <is>
+          <t>72180</t>
+        </is>
+      </c>
+      <c r="T398" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U398" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -32827,6 +36799,16 @@
       </c>
       <c r="S399" t="inlineStr">
         <is>
+          <t>72673 VIRGEN DE LA MEDALLA MILAGROSA</t>
+        </is>
+      </c>
+      <c r="T399" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U399" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -32908,6 +36890,16 @@
       </c>
       <c r="S400" t="inlineStr">
         <is>
+          <t>72425</t>
+        </is>
+      </c>
+      <c r="T400" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U400" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -32989,6 +36981,16 @@
       </c>
       <c r="S401" t="inlineStr">
         <is>
+          <t>72425</t>
+        </is>
+      </c>
+      <c r="T401" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U401" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -33070,6 +37072,16 @@
       </c>
       <c r="S402" t="inlineStr">
         <is>
+          <t>MARISCAL ANDRES AVELINO CACERES/MARISCAL ANDRES AVELINO CACERES/MARISCAL ANDRES AVELINO CACERES</t>
+        </is>
+      </c>
+      <c r="T402" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U402" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -33151,6 +37163,16 @@
       </c>
       <c r="S403" t="inlineStr">
         <is>
+          <t>013 JESUS DE NAZARETH</t>
+        </is>
+      </c>
+      <c r="T403" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U403" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -33232,6 +37254,16 @@
       </c>
       <c r="S404" t="inlineStr">
         <is>
+          <t>053 SAGRADO CORAZON DE JESUS</t>
+        </is>
+      </c>
+      <c r="T404" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U404" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -33313,6 +37345,16 @@
       </c>
       <c r="S405" t="inlineStr">
         <is>
+          <t>VICTOR RAUL HAYA DE LA TORRE</t>
+        </is>
+      </c>
+      <c r="T405" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U405" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -33394,6 +37436,16 @@
       </c>
       <c r="S406" t="inlineStr">
         <is>
+          <t>127 JULIO SALVADOR IZQUIERDO PUELL/127 JULIO SALVADOR IZQUIERDO PUELL</t>
+        </is>
+      </c>
+      <c r="T406" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U406" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -33475,6 +37527,16 @@
       </c>
       <c r="S407" t="inlineStr">
         <is>
+          <t>104 INMACULADA CONCEPCION</t>
+        </is>
+      </c>
+      <c r="T407" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U407" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -33556,6 +37618,16 @@
       </c>
       <c r="S408" t="inlineStr">
         <is>
+          <t>64148</t>
+        </is>
+      </c>
+      <c r="T408" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U408" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -33637,6 +37709,16 @@
       </c>
       <c r="S409" t="inlineStr">
         <is>
+          <t>64148</t>
+        </is>
+      </c>
+      <c r="T409" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U409" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -33718,6 +37800,16 @@
       </c>
       <c r="S410" t="inlineStr">
         <is>
+          <t>529/65009</t>
+        </is>
+      </c>
+      <c r="T410" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U410" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -33799,6 +37891,16 @@
       </c>
       <c r="S411" t="inlineStr">
         <is>
+          <t>ANDRES AVELINO CACERES/ANDRES AVELINO CACERES/ANDRES AVELINO CACERES</t>
+        </is>
+      </c>
+      <c r="T411" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U411" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -33880,6 +37982,16 @@
       </c>
       <c r="S412" t="inlineStr">
         <is>
+          <t>PEDRO CELIS FLORES</t>
+        </is>
+      </c>
+      <c r="T412" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U412" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -33961,6 +38073,16 @@
       </c>
       <c r="S413" t="inlineStr">
         <is>
+          <t>22338</t>
+        </is>
+      </c>
+      <c r="T413" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U413" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -34042,6 +38164,16 @@
       </c>
       <c r="S414" t="inlineStr">
         <is>
+          <t>11636 JEAN PIAGET/11636 JEAN PIAGET</t>
+        </is>
+      </c>
+      <c r="T414" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U414" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -34123,6 +38255,16 @@
       </c>
       <c r="S415" t="inlineStr">
         <is>
+          <t>FRANCISCO BOLOGNESI CERVANTES</t>
+        </is>
+      </c>
+      <c r="T415" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U415" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -34204,6 +38346,16 @@
       </c>
       <c r="S416" t="inlineStr">
         <is>
+          <t>FRANCISCO BOLOGNESI CERVANTES</t>
+        </is>
+      </c>
+      <c r="T416" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="U416" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -34285,6 +38437,16 @@
       </c>
       <c r="S417" t="inlineStr">
         <is>
+          <t>11614/11614</t>
+        </is>
+      </c>
+      <c r="T417" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U417" t="inlineStr">
+        <is>
           <t>UGME</t>
         </is>
       </c>
@@ -34365,6 +38527,16 @@
         </is>
       </c>
       <c r="S418" t="inlineStr">
+        <is>
+          <t>11635 INCA PACHACUTEC</t>
+        </is>
+      </c>
+      <c r="T418" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="U418" t="inlineStr">
         <is>
           <t>UGME</t>
         </is>

--- a/output/bases_limpias/Grupo_03_MODULOS/df_ugme_modulares.xlsx
+++ b/output/bases_limpias/Grupo_03_MODULOS/df_ugme_modulares.xlsx
@@ -34887,15 +34887,47 @@
         <v>1</v>
       </c>
       <c r="K378" t="inlineStr"/>
-      <c r="L378" t="inlineStr"/>
-      <c r="M378" t="inlineStr"/>
-      <c r="N378" t="inlineStr"/>
-      <c r="O378" t="inlineStr"/>
-      <c r="P378" t="inlineStr"/>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="M378" t="inlineStr">
+        <is>
+          <t>SATIPO</t>
+        </is>
+      </c>
+      <c r="N378" t="inlineStr">
+        <is>
+          <t>PAMPA HERMOSA</t>
+        </is>
+      </c>
+      <c r="O378" t="inlineStr">
+        <is>
+          <t>MARIPOSA</t>
+        </is>
+      </c>
+      <c r="P378" t="inlineStr">
+        <is>
+          <t>120605</t>
+        </is>
+      </c>
       <c r="Q378" t="inlineStr"/>
-      <c r="R378" t="inlineStr"/>
-      <c r="S378" t="inlineStr"/>
-      <c r="T378" t="inlineStr"/>
+      <c r="R378" t="inlineStr">
+        <is>
+          <t>UGEL SATIPO</t>
+        </is>
+      </c>
+      <c r="S378" t="inlineStr">
+        <is>
+          <t>[30682 CARLOS NORIEGA JIMENEZ]</t>
+        </is>
+      </c>
+      <c r="T378" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
       <c r="U378" t="inlineStr">
         <is>
           <t>UGME</t>

--- a/output/bases_limpias/Grupo_03_MODULOS/df_ugme_modulares.xlsx
+++ b/output/bases_limpias/Grupo_03_MODULOS/df_ugme_modulares.xlsx
@@ -419,57 +419,57 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>N°</t>
+          <t>n</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Código Local</t>
+          <t>cod_local</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Código modular</t>
+          <t>cod_mod</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Grupo (Aula Domo, Aula Modular, Escuela Modular, Módulo SS.HH., Pararrayo, Redes Complementarias, etc.)</t>
+          <t>grupo_aula_domo_aula_modular_escuela_modular_modulo_ss_hh_pa</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Descripción del bien</t>
+          <t>descripcion_del_bien</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Fecha de entrega (o estimada) (PECOSA)</t>
+          <t>fecha_de_entrega_o_estimada_pecosa</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Estado (Instalado, Donado, etc.)</t>
+          <t>estado_instalado_donado_etc</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Capacidad operativa (solo Escuela Modular, Aula Modular y Aula Domo)</t>
+          <t>capacidad_operativa_solo_escuela_modular_aula_modular_y_aula</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Monto contractual (S/)</t>
+          <t>monto_contractual</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Total de bienes</t>
+          <t>total_de_bienes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Comentarios</t>
+          <t>comentario</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
